--- a/research/PMP_Pharma_Companies_USA.xlsx
+++ b/research/PMP_Pharma_Companies_USA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>https://www.jnj.com</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/200406/000020040626000016/jnj-20251228.htm</t>
         </is>
@@ -503,12 +503,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>https://www.pfizer.com</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/78003/000007800326000026/pfe-20251231.htm</t>
         </is>
@@ -535,12 +535,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>https://www.merck.com</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/310158/000031015826000063/mrk-20251231.htm</t>
         </is>
@@ -567,12 +567,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>https://www.unitedhealthgroup.com</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/731766/000073176626000062/unh-20251231.htm</t>
         </is>
@@ -599,12 +599,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>https://www.amgen.com</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/318154/000031815426000010/amgn-20251231.htm</t>
         </is>
@@ -631,12 +631,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>https://www.gilead.com</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/882095/000088209526000006/gild-20251231.htm</t>
         </is>
@@ -663,12 +663,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>https://www.biogen.com</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/875045/000087504526000013/biib-20251231.htm</t>
         </is>
@@ -695,12 +695,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://www.regeneron.com</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/872589/000087258926000008/regn-20251231.htm</t>
         </is>
@@ -727,12 +727,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://www.illumina.com</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1110803/000111080326000024/ilmn-20251228.htm</t>
         </is>
@@ -759,12 +759,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://www.vrtx.com</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/875320/000087532026000056/vrtx-20251231.htm</t>
         </is>
@@ -791,12 +791,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://www.celgene.com</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CELG</t>
         </is>
@@ -823,12 +823,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://www.abbvie.com</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1551152/000155115226000008/abbv-20251231.htm</t>
         </is>
@@ -855,12 +855,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://www.lilly.com</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/59478/000005947826000013/lly-20251231.htm</t>
         </is>
@@ -887,12 +887,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://www.bms.com</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/14272/000001427226000004/bmy-20251231.htm</t>
         </is>
@@ -919,12 +919,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://www.allergan.com</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=AGN</t>
         </is>
@@ -951,12 +951,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://www.incyte.com</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/879169/000087916926000010/incy-20251231.htm</t>
         </is>
@@ -983,12 +983,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://www.seattlegenetics.com</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=SGEN</t>
         </is>
@@ -1015,12 +1015,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://www.alnylam.com</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1178670/000162828026007497/alny-20251231.htm</t>
         </is>
@@ -1047,12 +1047,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>https://www.alexion.com</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ALXN</t>
         </is>
@@ -1079,12 +1079,12 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>https://www.exelixis.com</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/939767/000093976726000021/exel-20260102.htm</t>
         </is>
@@ -1103,7 +1103,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Incyte Genomics, Inc.</t>
+          <t>Foundation Medicine, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1111,26 +1111,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>https://www.incyte.com</t>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.foundationmedicine.com</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Offers employees development plans, challenging job assignments, and training opportunities as part of standard people programs | Provides tuition reimbursement to support continued education for its ~2,844 employees | Ties a portion (3%) of its annual bonus incentive program to company-wide ESG/people targets, per its Global Responsibility Report</t>
+          <t>Runs a formal People Manager Development Program (PMDP) required for all newly hired or promoted people managers, with emotional intelligence training as a core component | Gives individual contributors access to a large third-party digital course library plus facilitated development programs | Operates as an independent Roche Group affiliate (acquired 2018, ~1,700 employees) and can tap into Roche's broader learning infrastructure (e.g., Roche Diagnostics University)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Incyte FY2025 Form ARS/10-K and 2024 Global Responsibility Report</t>
+          <t>Foundation Medicine careers blog; Roche corporate careers/training pages</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Foundation Medicine, Inc.</t>
+          <t>GRAIL, Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1138,26 +1138,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>https://www.foundationmedicine.com</t>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.grail.com</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Runs a formal People Manager Development Program (PMDP) required for all newly hired or promoted people managers, with emotional intelligence training as a core component | Gives individual contributors access to a large third-party digital course library plus facilitated development programs | Operates as an independent Roche Group affiliate (acquired 2018, ~1,700 employees) and can tap into Roche's broader learning infrastructure (e.g., Roche Diagnostics University)</t>
+          <t>Requires mandatory unconscious-bias training for employees as part of onboarding/DEI programming | Runs a 'Culture Ambassador' program of employee volunteers who help shape and reinforce company culture and engagement | Positions itself on 'clear growth paths' and career development as a core retention pitch (spun off from Illumina in 2024, still a young standalone filer)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Foundation Medicine careers blog; Roche corporate careers/training pages</t>
+          <t>GRAIL careers site; Built In and Glassdoor employer profiles</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Illumina Ventures</t>
+          <t>Guardant Health, Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1165,26 +1165,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>https://www.illumina.com</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.guardanthealth.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576280/000157628026000013/gh-20251231.htm</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Runs 'Illumina University,' an internal training arm delivering in-depth online and on-site courses on products, technical skills, and professional topics, plus webinars and university partnerships | Offers structured leadership development programs alongside mentoring/coaching, certification programs, and tuition reimbursement for job-related education | Blends classroom, virtual, and e-learning formats so employees build both technical and soft-skill capabilities</t>
+          <t>offers standard biotech/diagnostics-industry onboarding, compliance, and lab/quality-system training given its clinical lab and commercial oncology operations | provides some form of career mentoring and manager-led professional growth support as part of its general benefits package | does not publicly disclose specific training hours, dollars invested, or named leadership-academy programs in its 10-K human capital section</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Illumina careers site; Illumina 2025 Corporate Responsibility Report</t>
+          <t>Guardant Health careers page; Glassdoor/employer-review summaries</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GRAIL, Inc.</t>
+          <t>Invitae Corporation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1192,26 +1197,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>https://www.grail.com</t>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.invitae.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=NVTA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Requires mandatory unconscious-bias training for employees as part of onboarding/DEI programming | Runs a 'Culture Ambassador' program of employee volunteers who help shape and reinforce company culture and engagement | Positions itself on 'clear growth paths' and career development as a core retention pitch (spun off from Illumina in 2024, still a young standalone filer)</t>
+          <t>given genetic testing/counseling work, prospect likely maintained regular clinical training sessions and continuing education access for genetic counselors and lab staff | maintained entry-level hiring pipelines paired with structured career-development programs before its 2024 Chapter 11 filing | relied on cross-training and mentoring rather than large formal corporate academies</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GRAIL careers site; Built In and Glassdoor employer profiles</t>
+          <t>Historical 10-Ks (2020-2021); Glassdoor/careers content â€” company filed Chapter 11 in 2024</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Guardant Health, Inc.</t>
+          <t>Myriad Genetics, Inc.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1219,31 +1229,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>https://www.guardanthealth.com</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1576280/000157628026000013/gh-20251231.htm</t>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.myriad.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/899923/000089992326000018/mygn-20251231.htm</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>offers standard biotech/diagnostics-industry onboarding, compliance, and lab/quality-system training given its clinical lab and commercial oncology operations | provides some form of career mentoring and manager-led professional growth support as part of its general benefits package | does not publicly disclose specific training hours, dollars invested, or named leadership-academy programs in its 10-K human capital section</t>
+          <t>Sponsors a formal training and mentoring program specifically for high-potential employees to build leadership skills and career development | Runs eight employee-led resource groups (ERGs) that double as peer learning and development networks across the ~2,700-employee workforce | 2025 internal survey showed 84% of employees rated Myriad a Great Place to Work</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guardant Health careers page; Glassdoor/employer-review summaries</t>
+          <t>Myriad Genetics FY2025 10-K, Human Capital section</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Invitae Corporation</t>
+          <t>Natera, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1251,31 +1261,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>https://www.invitae.com</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=NVTA</t>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.natera.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1604821/000110465926020881/ntra-20251231x10k.htm</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>given genetic testing/counseling work, prospect likely maintained regular clinical training sessions and continuing education access for genetic counselors and lab staff | maintained entry-level hiring pipelines paired with structured career-development programs before its 2024 Chapter 11 filing | relied on cross-training and mentoring rather than large formal corporate academies</t>
+          <t>Launched leadership roundtables in 2025 plus expanded personal development training, directly responding to findings from its 2024 employee survey | Operates a growing set of employee resource groups (ERGs) that function as professional-development and networking platforms | Pursuing a 2025 ESG goal requiring all people managers to complete annual diversity training</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Historical 10-Ks (2020-2021); Glassdoor/careers content â€” company filed Chapter 11 in 2024</t>
+          <t>Natera FY2025 10-K, Human Capital section</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Myriad Genetics, Inc.</t>
+          <t>Exact Sciences Corporation</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1283,31 +1293,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>https://www.myriad.com</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/899923/000089992326000018/mygn-20251231.htm</t>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.exactsciences.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=EXAS</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sponsors a formal training and mentoring program specifically for high-potential employees to build leadership skills and career development | Runs eight employee-led resource groups (ERGs) that double as peer learning and development networks across the ~2,700-employee workforce | 2025 internal survey showed 84% of employees rated Myriad a Great Place to Work</t>
+          <t>Invests in developmental capabilities spanning facilitated workshops, podcasts, eLearning modules, individual development plans, mentoring and coaching for employees at every career stage | Hosts an annual leadership summit that brings company leaders together for development and enrichment activities, plus a dedicated employee mentoring program | Workforce of roughly 7,100 full-time employees posted a 9% voluntary turnover rate, below the healthcare industry benchmark; also offers tuition reimbursement</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Myriad Genetics FY2025 10-K, Human Capital section</t>
+          <t>Exact Sciences FY2025 10-K, Human Capital section</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Natera, Inc.</t>
+          <t>Adverum Biotechnologies, Inc.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1315,31 +1325,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>https://www.natera.com</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1604821/000110465926020881/ntra-20251231x10k.htm</t>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.adverum.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ADVM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Launched leadership roundtables in 2025 plus expanded personal development training, directly responding to findings from its 2024 employee survey | Operates a growing set of employee resource groups (ERGs) that function as professional-development and networking platforms | Pursuing a 2025 ESG goal requiring all people managers to complete annual diversity training</t>
+          <t>Offers 'Adverum University,' a named internal program giving employees at all levels access to leadership and professional-skills development | Provides learning forums, work rotations, and management certificate programs as part of its structured development offerings | Small workforce (~155 FTEs) with an active human-capital metrics program tracking demographics, diversity, compensation/benefits and engagement</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Natera FY2025 10-K, Human Capital section</t>
+          <t>Adverum Biotechnologies FY2024 10-K, Human Capital Management section</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Exact Sciences Corporation</t>
+          <t>Aimmune Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1347,31 +1357,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>https://www.exactsciences.com</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=EXAS</t>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.aimmune.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=AIMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Invests in developmental capabilities spanning facilitated workshops, podcasts, eLearning modules, individual development plans, mentoring and coaching for employees at every career stage | Hosts an annual leadership summit that brings company leaders together for development and enrichment activities, plus a dedicated employee mentoring program | Workforce of roughly 7,100 full-time employees posted a 9% voluntary turnover rate, below the healthcare industry benchmark; also offers tuition reimbursement</t>
+          <t>small clinical-stage-turned-commercial specialty biopharma with limited formal L&amp;D infrastructure prior to 2020 Nestle acquisition | relied on scientific/medical conference attendance, cross-functional mentoring, and on-the-job training typical of niche allergy-therapeutics companies | any structured tuition reimbursement or certification support would have been folded into Nestle Health Science's broader corporate L&amp;D programs post-acquisition</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Exact Sciences FY2025 10-K, Human Capital section</t>
+          <t>No specifics found â€” defunct as standalone filer since 2020 Nestle acquisition</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Adverum Biotechnologies, Inc.</t>
+          <t>Alder Biopharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1379,31 +1389,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>https://www.adverum.com</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ADVM</t>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.alderbio.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ALDR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Offers 'Adverum University,' a named internal program giving employees at all levels access to leadership and professional-skills development | Provides learning forums, work rotations, and management certificate programs as part of its structured development offerings | Small workforce (~155 FTEs) with an active human-capital metrics program tracking demographics, diversity, compensation/benefits and engagement</t>
+          <t>~200-employee clinical-stage biopharma (migraine antibody therapeutics) with informal, on-the-job learning culture rather than named programs | employee reviews suggest strong peer-to-peer learning but no structured career-advancement or leadership-development framework | any tuition or certification support was ad hoc rather than a codified benefit, consistent with small biotechs pre-acquisition</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Adverum Biotechnologies FY2024 10-K, Human Capital Management section</t>
+          <t>Glassdoor/Indeed employee reviews â€” defunct as standalone filer since 2019 Lundbeck acquisition</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aimmune Therapeutics, Inc.</t>
+          <t>AnaptysBio, Inc.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1411,31 +1421,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>https://www.aimmune.com</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=AIMT</t>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.anaptysbio.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370053/000119312526088290/anab-20251231.htm</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>small clinical-stage-turned-commercial specialty biopharma with limited formal L&amp;D infrastructure prior to 2020 Nestle acquisition | relied on scientific/medical conference attendance, cross-functional mentoring, and on-the-job training typical of niche allergy-therapeutics companies | any structured tuition reimbursement or certification support would have been folded into Nestle Health Science's broader corporate L&amp;D programs post-acquisition</t>
+          <t>As of FY2018 10-K, AnaptysBio reported 78 full-time employees (60 in R&amp;D, 24 with MD/PhD credentials), reflecting a small, technically credentialed workforce typical of clinical-stage biotech | Company careers/employee-review sources describe a stated culture of professional growth and skills development, though no named internal training program or $ investment figure is disclosed | No tuition reimbursement, PMP/certification partnership, or specific training-hours metric could be located</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>No specifics found â€” defunct as standalone filer since 2020 Nestle acquisition</t>
+          <t>AnaptysBio FY2018/2017 10-K filings; Glassdoor/Built In employee reviews</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alder Biopharmaceuticals, Inc.</t>
+          <t>Aptinyx Inc.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1443,31 +1453,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>https://www.alderbio.com</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ALDR</t>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.aptinyx.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=APTX</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>~200-employee clinical-stage biopharma (migraine antibody therapeutics) with informal, on-the-job learning culture rather than named programs | employee reviews suggest strong peer-to-peer learning but no structured career-advancement or leadership-development framework | any tuition or certification support was ad hoc rather than a codified benefit, consistent with small biotechs pre-acquisition</t>
+          <t>small clinical-stage CNS-biotech with limited dedicated L&amp;D budget, especially amid its 2023-2024 wind-down | professional development consisted mainly of scientific training, conference participation, and informal skills-sharing among a lean R&amp;D-heavy staff | no evidence of tuition reimbursement or certification partnerships, consistent with a company that ultimately dissolved operations</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Glassdoor/Indeed employee reviews â€” defunct as standalone filer since 2019 Lundbeck acquisition</t>
+          <t>Employee reviews mention training only in general terms â€” company wound down ~2023-2024</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AnaptysBio, Inc.</t>
+          <t>Arena Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1475,31 +1485,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>https://www.anaptysbio.com</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1370053/000119312526088290/anab-20251231.htm</t>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.arenapharm.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ARNA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>As of FY2018 10-K, AnaptysBio reported 78 full-time employees (60 in R&amp;D, 24 with MD/PhD credentials), reflecting a small, technically credentialed workforce typical of clinical-stage biotech | Company careers/employee-review sources describe a stated culture of professional growth and skills development, though no named internal training program or $ investment figure is disclosed | No tuition reimbursement, PMP/certification partnership, or specific training-hours metric could be located</t>
+          <t>mid-size clinical/commercial-stage biopharma (GI and dermatology therapeutics) with more developed HR infrastructure than typical small biotech given its scale prior to 2022 Pfizer acquisition | leadership and management development existed informally through its executive/leadership team structure, but no named academy or certification program is publicly documented | post-acquisition, any formal training benefits would have been absorbed into Pfizer's much larger corporate L&amp;D infrastructure</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AnaptysBio FY2018/2017 10-K filings; Glassdoor/Built In employee reviews</t>
+          <t>No specifics found â€” defunct as standalone filer since 2022 Pfizer acquisition</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Aptinyx Inc.</t>
+          <t>Arrowhead Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,31 +1517,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>https://www.aptinyx.com</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=APTX</t>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.arrowheadpharma.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/879407/000087940725000029/arwr-20250930.htm</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>small clinical-stage CNS-biotech with limited dedicated L&amp;D budget, especially amid its 2023-2024 wind-down | professional development consisted mainly of scientific training, conference participation, and informal skills-sharing among a lean R&amp;D-heavy staff | no evidence of tuition reimbursement or certification partnerships, consistent with a company that ultimately dissolved operations</t>
+          <t>10-K human capital section states the company supports employee development through individualized development plans, mentoring, coaching, group training, and conference attendance | Offers tuition reimbursement and financial support for continuing education as part of its employee development package | A significant portion of Arrowhead's ~400 full-time employees hold advanced degrees, reflecting a hire-and-develop strategy centered on specialized biotech/pharma R&amp;D talent</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Employee reviews mention training only in general terms â€” company wound down ~2023-2024</t>
+          <t>Arrowhead Pharmaceuticals 10-K, Human Capital section</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Arena Pharmaceuticals, Inc.</t>
+          <t>Ascendis Pharma A/S</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1539,31 +1549,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>https://www.arenapharm.com</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ARNA</t>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.ascendispharma.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ASND</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>mid-size clinical/commercial-stage biopharma (GI and dermatology therapeutics) with more developed HR infrastructure than typical small biotech given its scale prior to 2022 Pfizer acquisition | leadership and management development existed informally through its executive/leadership team structure, but no named academy or certification program is publicly documented | post-acquisition, any formal training benefits would have been absorbed into Pfizer's much larger corporate L&amp;D infrastructure</t>
+          <t>as a Danish/US biopharma with a global Sustainability/ESG reporting framework established in 2022, Ascendis probably runs structured annual compliance training for new and existing employees | given its 1,000+ and growing headcount (1,189 employees at end of 2025), likely offers structured onboarding and role-based technical/GxP training | markets itself as offering employees room to 'grow and develop their skills,' though no specific budget, hours, or named program could be confirmed</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>No specifics found â€” defunct as standalone filer since 2022 Pfizer acquisition</t>
+          <t>Ascendis Pharma investor relations/careers pages</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Arrowhead Pharmaceuticals, Inc.</t>
+          <t>Audentes Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1571,31 +1581,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>https://www.arrowheadpharma.com</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/879407/000087940725000029/arwr-20250930.htm</t>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.audentestx.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1782303/000119312526097543/bold-20251231.htm</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10-K human capital section states the company supports employee development through individualized development plans, mentoring, coaching, group training, and conference attendance | Offers tuition reimbursement and financial support for continuing education as part of its employee development package | A significant portion of Arrowhead's ~400 full-time employees hold advanced degrees, reflecting a hire-and-develop strategy centered on specialized biotech/pharma R&amp;D talent</t>
+          <t>Audentes Therapeutics (acquired by Astellas in 2020, now Astellas Gene Therapies) no longer files as a standalone SEC reporter, so no independent recent training disclosures exist | as a rare-disease gene therapy company, probably relied on specialized scientific/technical training and cross-functional onboarding rather than published corporate L&amp;D programs | pre-acquisition employee feedback pointed to gaps in structured manager training, suggesting formal leadership-development programs were limited or informal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arrowhead Pharmaceuticals 10-K, Human Capital section</t>
+          <t>Pre-acquisition employee reviews and company history â€” not an independent SEC registrant since 2020</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ascendis Pharma A/S</t>
+          <t>Autolus Therapeutics plc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1603,31 +1613,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>https://www.ascendispharma.com</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ASND</t>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.autolustherapeutics.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1730463/000173046326000038/autl-20251231.htm</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>as a Danish/US biopharma with a global Sustainability/ESG reporting framework established in 2022, Ascendis probably runs structured annual compliance training for new and existing employees | given its 1,000+ and growing headcount (1,189 employees at end of 2025), likely offers structured onboarding and role-based technical/GxP training | markets itself as offering employees room to 'grow and develop their skills,' though no specific budget, hours, or named program could be confirmed</t>
+          <t>States it is committed to supporting employees through learning and development programs, alongside reward/recognition, hybrid working, and employee resource groups | New hires report being trained thoroughly through onboarding, described by staff as being taught 'every step of the way' | as a UK-based clinical-stage cell therapy company filing 20-Fs, probably includes a Human Capital Resources section referencing training investment, but no specific figures could be confirmed</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ascendis Pharma investor relations/careers pages</t>
+          <t>Autolus Therapeutics careers/culture pages</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Audentes Therapeutics, Inc.</t>
+          <t>Blueprint Medicines Corporation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1635,31 +1645,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>https://www.audentestx.com</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1782303/000119312526097543/bold-20251231.htm</t>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.blueprintmedicines.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=BPMC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audentes Therapeutics (acquired by Astellas in 2020, now Astellas Gene Therapies) no longer files as a standalone SEC reporter, so no independent recent training disclosures exist | as a rare-disease gene therapy company, probably relied on specialized scientific/technical training and cross-functional onboarding rather than published corporate L&amp;D programs | pre-acquisition employee feedback pointed to gaps in structured manager training, suggesting formal leadership-development programs were limited or informal</t>
+          <t>Maintained a dedicated Learning &amp; Development team and offered job training, conferences, mentorship programs, lunch-and-learns, tuition reimbursement, and an apprenticeship program letting employees rotate across company functions | An internal employee engagement survey showed an 80% positive score on managers actively supporting employees' career aspirations | Managers had access to a dedicated development tool tracking employee competencies and development goals</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pre-acquisition employee reviews and company history â€” not an independent SEC registrant since 2020</t>
+          <t>Culture Amp case study on Blueprint Medicines' L&amp;D programs; Glassdoor benefits listings (pre-Sanofi acquisition)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Autolus Therapeutics plc</t>
+          <t>C4 Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1667,31 +1677,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>https://www.autolustherapeutics.com</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1730463/000173046326000038/autl-20251231.htm</t>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.c4therapeutics.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662579/000162828026012000/cccc-20251231.htm</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>States it is committed to supporting employees through learning and development programs, alongside reward/recognition, hybrid working, and employee resource groups | New hires report being trained thoroughly through onboarding, described by staff as being taught 'every step of the way' | as a UK-based clinical-stage cell therapy company filing 20-Fs, probably includes a Human Capital Resources section referencing training investment, but no specific figures could be confirmed</t>
+          <t>104 full-time employees as of Dec 31 2025, including 40 with M.D./Ph.D. degrees, per FY2025 10-K Human Capital Resources section | Offers development programs enabling continued learning and growth as part of employment package, plus ongoing investment in employee development for retention | Trains leaders and staff on inclusive workplace and equitable pay practices as part of culture initiatives</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Autolus Therapeutics careers/culture pages</t>
+          <t>C4 Therapeutics FY2025 10-K, Human Capital Resources section</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Blueprint Medicines Corporation</t>
+          <t>Cara Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1699,31 +1709,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>https://www.blueprintmedicines.com</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=BPMC</t>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.caratherapeutics.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CARA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maintained a dedicated Learning &amp; Development team and offered job training, conferences, mentorship programs, lunch-and-learns, tuition reimbursement, and an apprenticeship program letting employees rotate across company functions | An internal employee engagement survey showed an 80% positive score on managers actively supporting employees' career aspirations | Managers had access to a dedicated development tool tracking employee competencies and development goals</t>
+          <t>given Cara's severe 2024 workforce reduction (from ~106 employees to about 10 by March 2025), formal L&amp;D programs were almost certainly curtailed | prior to the 2024 restructuring, human capital approach centered on equity/cash incentives rather than named training programs, typical of small clinical-stage biotechs | as a skeleton-crew clinical company post-restructuring, remaining professional development spend would be ad hoc rather than a structured program</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Culture Amp case study on Blueprint Medicines' L&amp;D programs; Glassdoor benefits listings (pre-Sanofi acquisition)</t>
+          <t>Cara Therapeutics 10-Ks â€” no specific training program disclosures found</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C4 Therapeutics, Inc.</t>
+          <t>Cardiff Oncology, Inc.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1731,31 +1741,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>https://www.c4therapeutics.com</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1662579/000162828026012000/cccc-20251231.htm</t>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.cardiffoncology.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1213037/000119312526067464/crdf-20251231.htm</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>104 full-time employees as of Dec 31 2025, including 40 with M.D./Ph.D. degrees, per FY2025 10-K Human Capital Resources section | Offers development programs enabling continued learning and growth as part of employment package, plus ongoing investment in employee development for retention | Trains leaders and staff on inclusive workplace and equitable pay practices as part of culture initiatives</t>
+          <t>31 total employees (30 full-time) as of Feb 19, 2026, per FY2025 10-K Human Capital section | States company is committed to supporting employees' professional development as a stated human capital objective, with no specific program names, hours, or dollar figures disclosed | Competitive compensation and benefits, not tuition reimbursement or named academies, are the primary cited retention levers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C4 Therapeutics FY2025 10-K, Human Capital Resources section</t>
+          <t>Cardiff Oncology FY2025 10-K, Human Capital section</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cara Therapeutics, Inc.</t>
+          <t>Catalyst Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1763,31 +1773,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>https://www.caratherapeutics.com</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CARA</t>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.catalystpharma.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1369568/000119312526071525/cprx-20251231.htm</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>given Cara's severe 2024 workforce reduction (from ~106 employees to about 10 by March 2025), formal L&amp;D programs were almost certainly curtailed | prior to the 2024 restructuring, human capital approach centered on equity/cash incentives rather than named training programs, typical of small clinical-stage biotechs | as a skeleton-crew clinical company post-restructuring, remaining professional development spend would be ad hoc rather than a structured program</t>
+          <t>182 employees as of Feb 23, 2026 (128 commercial, 8 R&amp;D), per FY2025 10-K | Workforce Goals section cites recruitment, hiring, development, training, compensation and advancement based on qualifications/performance, plus annual mandatory training on preventing discrimination/harassment | Employee training referenced mainly in cybersecurity/compliance governance context, not as a dedicated professional-development or certification initiative</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cara Therapeutics 10-Ks â€” no specific training program disclosures found</t>
+          <t>Catalyst Pharmaceuticals FY2025 10-K, Human Capital/Workforce Goals sections</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cardiff Oncology, Inc.</t>
+          <t>Celyad SA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1795,31 +1805,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>https://www.cardiffoncology.com</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1213037/000119312526067464/crdf-20251231.htm</t>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.celyad.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CYAD</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>31 total employees (30 full-time) as of Feb 19, 2026, per FY2025 10-K Human Capital section | States company is committed to supporting employees' professional development as a stated human capital objective, with no specific program names, hours, or dollar figures disclosed | Competitive compensation and benefits, not tuition reimbursement or named academies, are the primary cited retention levers</t>
+          <t>as a small Belgium-based clinical-stage biotech, Celyad probably runs standard compliance/safety training rather than a formal L&amp;D or certification-reimbursement program | given restructuring history (manufacturing transferred to Cellistic in 2022-2023) and lean headcount, structured leadership-development or tuition-assistance programs are improbable at this scale | any professional development is informal/on-the-job, consistent with a research-focused CAR T biotech</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cardiff Oncology FY2025 10-K, Human Capital section</t>
+          <t>Celyad Oncology SA Form 20-F â€” no specific training/L&amp;D program disclosed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Catalyst Pharmaceuticals, Inc.</t>
+          <t>Chimerix, Inc.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1827,31 +1837,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>https://www.catalystpharma.com</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1369568/000119312526071525/cprx-20251231.htm</t>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.chimerix.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CMRX</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>182 employees as of Feb 23, 2026 (128 commercial, 8 R&amp;D), per FY2025 10-K | Workforce Goals section cites recruitment, hiring, development, training, compensation and advancement based on qualifications/performance, plus annual mandatory training on preventing discrimination/harassment | Employee training referenced mainly in cybersecurity/compliance governance context, not as a dedicated professional-development or certification initiative</t>
+          <t>as a small clinical/commercial-stage biopharma (~100-150 employees historically), Chimerix likely relies on informal on-the-job mentoring and conference attendance rather than a large formal L&amp;D department | offers standard biotech benefits that may include tuition assistance or professional-development stipends for R&amp;D, regulatory, and commercial staff | leadership and compliance training (GxP, pharmacovigilance) is probable given its FDA-regulated antiviral business, but no dollar figures or training-hour metrics are disclosed</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Catalyst Pharmaceuticals FY2025 10-K, Human Capital/Workforce Goals sections</t>
+          <t>Chimerix 10-K filings; careers pages â€” no specific training program disclosed</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Celyad SA</t>
+          <t>Clovis Oncology, Inc.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1859,31 +1869,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>https://www.celyad.com</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CYAD</t>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.clovisoncology.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CLVS</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>as a small Belgium-based clinical-stage biotech, Celyad probably runs standard compliance/safety training rather than a formal L&amp;D or certification-reimbursement program | given restructuring history (manufacturing transferred to Cellistic in 2022-2023) and lean headcount, structured leadership-development or tuition-assistance programs are improbable at this scale | any professional development is informal/on-the-job, consistent with a research-focused CAR T biotech</t>
+          <t>prior to its December 2022 Chapter 11 filing, Clovis Oncology's 10-K human capital section referenced commitment to employee retention, growth and development and an inclusive culture, but named no specific certification or tuition program | as with many commercial-stage oncology biotechs, Clovis probably supported compliance training and manager training rather than a structured PMP-style certification track | conducted respectful-workplace/anti-bias training and pay-gap assessments pre-bankruptcy, but company is now defunct</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Celyad Oncology SA Form 20-F â€” no specific training/L&amp;D program disclosed</t>
+          <t>Clovis Oncology 10-K FY2021 human capital section â€” company entered Chapter 11 bankruptcy Dec 2022, now defunct</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Chimerix, Inc.</t>
+          <t>Coherus Biosciences, Inc.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1891,31 +1901,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>https://www.chimerix.com</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CMRX</t>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.coherus.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512762/000110465926025308/chrs-20251231x10k.htm</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>as a small clinical/commercial-stage biopharma (~100-150 employees historically), Chimerix likely relies on informal on-the-job mentoring and conference attendance rather than a large formal L&amp;D department | offers standard biotech benefits that may include tuition assistance or professional-development stipends for R&amp;D, regulatory, and commercial staff | leadership and compliance training (GxP, pharmacovigilance) is probable given its FDA-regulated antiviral business, but no dollar figures or training-hour metrics are disclosed</t>
+          <t>Coherus BioSciences' 10-K human capital disclosures and careers pages emphasize competitive compensation/benefits and equity incentive awards to attract and retain talent, but no named training program, tuition benefit, or certification partnership was found | as a commercial-stage immuno-oncology/biosimilars company, Coherus probably provides standard onboarding, compliance training, and manager development | employee review sites show mixed feedback on growth/learning opportunities, suggesting no widely publicized structured L&amp;D or leadership-academy program</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chimerix 10-K filings; careers pages â€” no specific training program disclosed</t>
+          <t>Coherus BioSciences 10-K FY2025 filing excerpts; Built In/Indeed careers reviews</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clovis Oncology, Inc.</t>
+          <t>Corvus Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1923,31 +1933,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>https://www.clovisoncology.com</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=CLVS</t>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.corvuspharma.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1626971/000110465926027047/crvs-20251231x10k.htm</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>prior to its December 2022 Chapter 11 filing, Clovis Oncology's 10-K human capital section referenced commitment to employee retention, growth and development and an inclusive culture, but named no specific certification or tuition program | as with many commercial-stage oncology biotechs, Clovis probably supported compliance training and manager training rather than a structured PMP-style certification track | conducted respectful-workplace/anti-bias training and pay-gap assessments pre-bankruptcy, but company is now defunct</t>
+          <t>FY2024 10-K human capital section states objectives include identifying, recruiting, retaining, incentivizing and integrating employees via competitive compensation/benefits, with no named training or certification program disclosed | As of Dec 31, 2024, Corvus had only 31 total employees (23 in R&amp;D), too small a headcount to support a dedicated corporate training department | Compensation strategy combines base salary, cash bonuses, and equity awards as primary retention/motivation tools, with no tuition reimbursement or certification partnership mentioned</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Clovis Oncology 10-K FY2021 human capital section â€” company entered Chapter 11 bankruptcy Dec 2022, now defunct</t>
+          <t>Corvus Pharmaceuticals 10-K FY2024/2025, human capital resources section</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Coherus Biosciences, Inc.</t>
+          <t>CytomX Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1955,31 +1965,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>https://www.coherus.com</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1512762/000110465926025308/chrs-20251231x10k.htm</t>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.cytomx.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1501989/000119312526107146/ctmx-20251231.htm</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coherus BioSciences' 10-K human capital disclosures and careers pages emphasize competitive compensation/benefits and equity incentive awards to attract and retain talent, but no named training program, tuition benefit, or certification partnership was found | as a commercial-stage immuno-oncology/biosimilars company, Coherus probably provides standard onboarding, compliance training, and manager development | employee review sites show mixed feedback on growth/learning opportunities, suggesting no widely publicized structured L&amp;D or leadership-academy program</t>
+          <t>10-K human capital section states objectives include identifying, recruiting, retaining, incentivizing and integrating employees, with equity incentive plans designed to attract, retain and motivate staff, but no named training program or tuition benefit disclosed | As of Dec 31, 2020, CytomX had 144 full-time plus 2 part-time employees, with 109 primarily in R&amp;D, indicating a clinical-stage scale unlikely to support a large internal certification/leadership academy | Reports no unionized workforce and describes employee relations as good</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coherus BioSciences 10-K FY2025 filing excerpts; Built In/Indeed careers reviews</t>
+          <t>CytomX Therapeutics 10-K FY2020/FY2025, human capital resources section</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Corvus Pharmaceuticals, Inc.</t>
+          <t>Deciphera Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1987,31 +1997,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>https://www.corvuspharma.com</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1626971/000110465926027047/crvs-20251231x10k.htm</t>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.deciphera.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=DCPH</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FY2024 10-K human capital section states objectives include identifying, recruiting, retaining, incentivizing and integrating employees via competitive compensation/benefits, with no named training or certification program disclosed | As of Dec 31, 2024, Corvus had only 31 total employees (23 in R&amp;D), too small a headcount to support a dedicated corporate training department | Compensation strategy combines base salary, cash bonuses, and equity awards as primary retention/motivation tools, with no tuition reimbursement or certification partnership mentioned</t>
+          <t>as a formerly independent oncology biotech (acquired by ONO Pharmaceutical in 2024), Deciphera likely offered informal on-the-job scientific/technical training typical of small-cap biotech rather than large formal L&amp;D programs | published a 2021 ESG report referencing general employee development commitments, but specific training metrics are not publicly available and the entity is no longer an independent SEC filer | post-acquisition, any legacy training programs would have been folded into ONO Pharmaceutical's broader corporate L&amp;D infrastructure</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Corvus Pharmaceuticals 10-K FY2024/2025, human capital resources section</t>
+          <t>Deciphera 10-K FY2019, 2021 ESG report reference â€” company defunct/absorbed post-2024 ONO acquisition</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CytomX Therapeutics, Inc.</t>
+          <t>Denali Therapeutics Inc.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2019,31 +2029,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>https://www.cytomx.com</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1501989/000119312526107146/ctmx-20251231.htm</t>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.denalitherapeutics.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1714899/000171489926000021/dnli-20251231.htm</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>10-K human capital section states objectives include identifying, recruiting, retaining, incentivizing and integrating employees, with equity incentive plans designed to attract, retain and motivate staff, but no named training program or tuition benefit disclosed | As of Dec 31, 2020, CytomX had 144 full-time plus 2 part-time employees, with 109 primarily in R&amp;D, indicating a clinical-stage scale unlikely to support a large internal certification/leadership academy | Reports no unionized workforce and describes employee relations as good</t>
+          <t>10-K human capital section states Denali believes training and development are an important part of creating a safe, productive, fair, and equal environment | Human capital strategy explicitly aims to attract new talent and retain/incentivize existing employees by investing in their professional development, offering challenging and rewarding opportunities for personal growth | ~422 full-time employees as of Dec 31, 2024; employee reviews indicate tuition assistance is offered though not detailed by name in SEC filings</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CytomX Therapeutics 10-K FY2020/FY2025, human capital resources section</t>
+          <t>Denali Therapeutics 10-K filings (FY2021-FY2025); Glassdoor employee benefits data</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deciphera Pharmaceuticals, Inc.</t>
+          <t>Eiger BioPharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2051,31 +2061,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>https://www.deciphera.com</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=DCPH</t>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.eigerbio.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=EIGR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>as a formerly independent oncology biotech (acquired by ONO Pharmaceutical in 2024), Deciphera likely offered informal on-the-job scientific/technical training typical of small-cap biotech rather than large formal L&amp;D programs | published a 2021 ESG report referencing general employee development commitments, but specific training metrics are not publicly available and the entity is no longer an independent SEC filer | post-acquisition, any legacy training programs would have been folded into ONO Pharmaceutical's broader corporate L&amp;D infrastructure</t>
+          <t>Eiger filed for Chapter 11 bankruptcy in 2023 and wound down operations, so no current or recent formal L&amp;D program exists | as a rare-disease biotech with a small headcount (~26-28 employees pre-bankruptcy), training was likely informal, role-specific rather than a structured corporate program | post-bankruptcy asset sales mean remaining staff were absorbed by acquiring entities with their own onboarding/training processes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deciphera 10-K FY2019, 2021 ESG report reference â€” company defunct/absorbed post-2024 ONO acquisition</t>
+          <t>Company news/press releases on 2023 Chapter 11 filing</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Denali Therapeutics Inc.</t>
+          <t>Epizyme, Inc.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2083,31 +2093,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>https://www.denalitherapeutics.com</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1714899/000171489926000021/dnli-20251231.htm</t>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.epizyme.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=EPZM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>10-K human capital section states Denali believes training and development are an important part of creating a safe, productive, fair, and equal environment | Human capital strategy explicitly aims to attract new talent and retain/incentivize existing employees by investing in their professional development, offering challenging and rewarding opportunities for personal growth | ~422 full-time employees as of Dec 31, 2024; employee reviews indicate tuition assistance is offered though not detailed by name in SEC filings</t>
+          <t>Pre-acquisition (by Ipsen, 2022) 10-K human capital disclosures described a culture built on 'EpiExcellence' attributes including innovation with continuous learning as a core cultural pillar | Company had 304 full-time employees as of Feb 2021, with 94 in R&amp;D, emphasizing workplace community/culture rather than naming specific formal training programs | post-2022 Ipsen acquisition, employees transitioned to Ipsen's corporate L&amp;D framework</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Denali Therapeutics 10-K filings (FY2021-FY2025); Glassdoor employee benefits data</t>
+          <t>Epizyme 10-K FY2020 â€” company acquired by Ipsen in 2022, no longer independent filer</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Eiger BioPharmaceuticals, Inc.</t>
+          <t>Fate Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2115,31 +2125,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>https://www.eigerbio.com</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=EIGR</t>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.fatetherapeutics.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1434316/000119312526073699/fate-20251231.htm</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Eiger filed for Chapter 11 bankruptcy in 2023 and wound down operations, so no current or recent formal L&amp;D program exists | as a rare-disease biotech with a small headcount (~26-28 employees pre-bankruptcy), training was likely informal, role-specific rather than a structured corporate program | post-bankruptcy asset sales mean remaining staff were absorbed by acquiring entities with their own onboarding/training processes</t>
+          <t>10-K human capital section states Fate invests in and develops all levels of employees via ongoing technical training, career pathing, professional development, and targeted leadership development programs for frontline leaders through executive leadership programs | Employees guided by the company's 'Pathways to Success'/'The Fate Way' framework, including ongoing Career Development Workshops with individual development plans encouraged for all staff | Offers professional, management and leadership development training programs to help employees develop cross-functional skills</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Company news/press releases on 2023 Chapter 11 filing</t>
+          <t>Fate Therapeutics 10-K (FY2024/FY2025); Fate Therapeutics careers/culture site</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Epizyme, Inc.</t>
+          <t>Five Prime Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2147,31 +2157,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>https://www.epizyme.com</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=EPZM</t>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.fiveprime.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=FPRX</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pre-acquisition (by Ipsen, 2022) 10-K human capital disclosures described a culture built on 'EpiExcellence' attributes including innovation with continuous learning as a core cultural pillar | Company had 304 full-time employees as of Feb 2021, with 94 in R&amp;D, emphasizing workplace community/culture rather than naming specific formal training programs | post-2022 Ipsen acquisition, employees transitioned to Ipsen's corporate L&amp;D framework</t>
+          <t>acquired by Amgen in 2021 and no longer files as standalone public company, so no current SEC/investor disclosures on training exist | as a small clinical-stage biotech (~100-150 employees pre-acquisition), L&amp;D was probably informal, built around scientific conference attendance and on-the-job mentoring rather than formal certification programs | post-acquisition, remaining staff were folded into Amgen's corporate L&amp;D and leadership-development infrastructure</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Epizyme 10-K FY2020 â€” company acquired by Ipsen in 2022, no longer independent filer</t>
+          <t>No standalone filings found post-2021 Amgen acquisition</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Fate Therapeutics, Inc.</t>
+          <t>Flexion Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2179,31 +2189,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>https://www.fatetherapeutics.com</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1434316/000119312526073699/fate-20251231.htm</t>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.flexiontherapeutics.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=FLXN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>10-K human capital section states Fate invests in and develops all levels of employees via ongoing technical training, career pathing, professional development, and targeted leadership development programs for frontline leaders through executive leadership programs | Employees guided by the company's 'Pathways to Success'/'The Fate Way' framework, including ongoing Career Development Workshops with individual development plans encouraged for all staff | Offers professional, management and leadership development training programs to help employees develop cross-functional skills</t>
+          <t>acquired by Pacira BioSciences in 2021 and delisted, so no current 10-K/ESG training disclosures are available | pre-acquisition employee feedback suggested limited formal career-advancement structure, consistent with a lean commercial-stage biotech focused on one product (Zilretta) | standard benefits existed, but no evidence of named leadership academies or certification/tuition programs was found</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fate Therapeutics 10-K (FY2024/FY2025); Fate Therapeutics careers/culture site</t>
+          <t>Public employee review sites â€” no post-2021 standalone corporate filings exist</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Five Prime Therapeutics, Inc.</t>
+          <t>G1 Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2211,31 +2221,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>https://www.fiveprime.com</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=FPRX</t>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.g1therapeutics.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=GTHX</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>acquired by Amgen in 2021 and no longer files as standalone public company, so no current SEC/investor disclosures on training exist | as a small clinical-stage biotech (~100-150 employees pre-acquisition), L&amp;D was probably informal, built around scientific conference attendance and on-the-job mentoring rather than formal certification programs | post-acquisition, remaining staff were folded into Amgen's corporate L&amp;D and leadership-development infrastructure</t>
+          <t>SEC 10-K filings disclose headcount by function (e.g., 104 employees, 75 in R&amp;D as of FY2019) but do not include specific training-hour, tuition-reimbursement, or certification-program figures | as a commercial-stage oncology biopharma, G1 probably relies on informal scientific/clinical training, conference attendance, and standard onboarding rather than a named corporate academy | careers page emphasizes a collaborative, inclusive culture, but no concrete L&amp;D investment numbers are published</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>No standalone filings found post-2021 Amgen acquisition</t>
+          <t>G1 Therapeutics 10-K filings (FY2017-FY2023); G1 careers page</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Flexion Therapeutics, Inc.</t>
+          <t>Galapagos NV</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2243,31 +2253,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>https://www.flexiontherapeutics.com</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=FLXN</t>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.glpg.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=GLPG</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>acquired by Pacira BioSciences in 2021 and delisted, so no current 10-K/ESG training disclosures are available | pre-acquisition employee feedback suggested limited formal career-advancement structure, consistent with a lean commercial-stage biotech focused on one product (Zilretta) | standard benefits existed, but no evidence of named leadership academies or certification/tuition programs was found</t>
+          <t>In 2023, Galapagos employees and leaders attended more than 4,500 internal learning and development events (excluding compliance training, conferences, and on-the-job learning) | Nearly 50 managers received over 2,500 hours of individual leadership coaching from external consultants in 2023, alongside structured programs like the annual 'Talent Cycle' reviews and 'Talent Talks' development sessions | In 2024, Galapagos rolled out new compliance/ethics training integrated into broader leadership training, with 94% of employees completing the updated Code of Conduct training</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Public employee review sites â€” no post-2021 standalone corporate filings exist</t>
+          <t>Galapagos NV Annual Report 2023 and 2024 Sustainability/ESG sections</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>G1 Therapeutics, Inc.</t>
+          <t>Global Blood Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2275,31 +2285,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>https://www.g1therapeutics.com</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=GTHX</t>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.globalbloodtherapeutics.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=GBT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SEC 10-K filings disclose headcount by function (e.g., 104 employees, 75 in R&amp;D as of FY2019) but do not include specific training-hour, tuition-reimbursement, or certification-program figures | as a commercial-stage oncology biopharma, G1 probably relies on informal scientific/clinical training, conference attendance, and standard onboarding rather than a named corporate academy | careers page emphasizes a collaborative, inclusive culture, but no concrete L&amp;D investment numbers are published</t>
+          <t>acquired by Pfizer in 2022 and no longer files independently, so no current standalone training disclosures exist | pre-acquisition employee reviews rated career opportunities highly (4.6/5 on Glassdoor) and culture/values at 4.8/5, suggesting an above-average internal development environment for a mid-cap biotech focused on sickle cell disease therapies | post-acquisition, former GBT staff gained access to Pfizer's much larger corporate L&amp;D, leadership-development, and tuition-support infrastructure</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>G1 Therapeutics 10-K filings (FY2017-FY2023); G1 careers page</t>
+          <t>Glassdoor employee reviews (pre-2022); Pfizer acquisition announcement</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Galapagos NV</t>
+          <t>Globus Medical, Inc.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2307,31 +2317,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>https://www.glpg.com</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=GLPG</t>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.globusmedical.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1237831/000162828026011209/gmed-20251231.htm</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>In 2023, Galapagos employees and leaders attended more than 4,500 internal learning and development events (excluding compliance training, conferences, and on-the-job learning) | Nearly 50 managers received over 2,500 hours of individual leadership coaching from external consultants in 2023, alongside structured programs like the annual 'Talent Cycle' reviews and 'Talent Talks' development sessions | In 2024, Galapagos rolled out new compliance/ethics training integrated into broader leadership training, with 94% of employees completing the updated Code of Conduct training</t>
+          <t>Robust onboarding program for new hires covering full product portfolio, company history, and underlying medical conditions its devices treat | Offers tuition reimbursement to all eligible employees and stock option participation to all eligible employees | Maintains ongoing leadership training programs plus dedicated Sales Trainer team and mandatory compliance/ethics training for all employees and third-party distributors</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Galapagos NV Annual Report 2023 and 2024 Sustainability/ESG sections</t>
+          <t>Globus Medical FY2025 10-K (SEC EDGAR) human capital section</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Global Blood Therapeutics, Inc.</t>
+          <t>Harpoon Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2339,31 +2349,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>https://www.globalbloodtherapeutics.com</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=GBT</t>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.harpoontx.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=HARP</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>acquired by Pfizer in 2022 and no longer files independently, so no current standalone training disclosures exist | pre-acquisition employee reviews rated career opportunities highly (4.6/5 on Glassdoor) and culture/values at 4.8/5, suggesting an above-average internal development environment for a mid-cap biotech focused on sickle cell disease therapies | post-acquisition, former GBT staff gained access to Pfizer's much larger corporate L&amp;D, leadership-development, and tuition-support infrastructure</t>
+          <t>acquired by Merck in 2024 and absorbed into Merck's oncology R&amp;D organization, so no longer files as a standalone public company | as a former clinical-stage biotech, probably ran standard scientific/GxP compliance training and small-team mentorship rather than large formal L&amp;D programs | any tuition or certification support (if it existed) would now fall under Merck's broader corporate learning and development umbrella</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Glassdoor employee reviews (pre-2022); Pfizer acquisition announcement</t>
+          <t>Public knowledge of 2024 Merck acquisition â€” no standalone filings available</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Globus Medical, Inc.</t>
+          <t>Heritage Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2371,31 +2381,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>https://www.globusmedical.com</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1237831/000162828026011209/gmed-20251231.htm</t>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.heritagepharma.com</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Robust onboarding program for new hires covering full product portfolio, company history, and underlying medical conditions its devices treat | Offers tuition reimbursement to all eligible employees and stock option participation to all eligible employees | Maintains ongoing leadership training programs plus dedicated Sales Trainer team and mandatory compliance/ethics training for all employees and third-party distributors</t>
+          <t>as a mid-size specialty/generic pharma manufacturer, probably provides mandatory GMP and quality/regulatory compliance training for plant and QA staff | relies on informal mentorship and cross-functional on-the-job training for new hires rather than a named corporate university or leadership academy | being privately held with no public ESG/annual report, offers standard onboarding plus role-specific technical training but no disclosed tuition reimbursement or PMP-style certification program</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Globus Medical FY2025 10-K (SEC EDGAR) human capital section</t>
+          <t>Company careers page and industry norms for privately held generics manufacturers</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Harpoon Therapeutics, Inc.</t>
+          <t>Homology Medicines, Inc.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2403,31 +2408,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>https://www.harpoontx.com</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=HARP</t>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.homologymedicines.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=FIXX</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>acquired by Merck in 2024 and absorbed into Merck's oncology R&amp;D organization, so no longer files as a standalone public company | as a former clinical-stage biotech, probably ran standard scientific/GxP compliance training and small-team mentorship rather than large formal L&amp;D programs | any tuition or certification support (if it existed) would now fall under Merck's broader corporate learning and development umbrella</t>
+          <t>underwent an 87% workforce reduction in 2023 and merged into Q32 Bio in 2024, so it no longer operates as an independent employer with its own training programs | prior to the reset, as a clinical-stage gene-therapy biotech it probably offered standard lab-safety, GxP, and scientific compliance training rather than broad corporate L&amp;D initiatives | any remaining professional development support would now be governed by Q32 Bio's employment policies post-merger</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Public knowledge of 2024 Merck acquisition â€” no standalone filings available</t>
+          <t>Public reporting on 2023 layoffs and 2023-2024 Q32 Bio reverse merger</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Heritage Pharmaceuticals, Inc.</t>
+          <t>Ignyta, Inc.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2435,26 +2440,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>https://www.heritagepharma.com</t>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.ignyta.com</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>as a mid-size specialty/generic pharma manufacturer, probably provides mandatory GMP and quality/regulatory compliance training for plant and QA staff | relies on informal mentorship and cross-functional on-the-job training for new hires rather than a named corporate university or leadership academy | being privately held with no public ESG/annual report, offers standard onboarding plus role-specific technical training but no disclosed tuition reimbursement or PMP-style certification program</t>
+          <t>acquired by Roche/Genentech in 2018 and dissolved as an independent entity, so it has not filed or disclosed L&amp;D programs in years | as a small clinical-stage oncology biotech pre-acquisition, probably offered basic scientific/compliance training typical of that stage rather than a formal training department | any legacy employees' professional development is now handled entirely under Roche/Genentech's corporate learning framework</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Company careers page and industry norms for privately held generics manufacturers</t>
+          <t>Public knowledge of 2018 Roche acquisition</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Homology Medicines, Inc.</t>
+          <t>Innate Pharma S.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2462,31 +2467,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>https://www.homologymedicines.com</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=FIXX</t>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.innate-pharma.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=IPHA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>underwent an 87% workforce reduction in 2023 and merged into Q32 Bio in 2024, so it no longer operates as an independent employer with its own training programs | prior to the reset, as a clinical-stage gene-therapy biotech it probably offered standard lab-safety, GxP, and scientific compliance training rather than broad corporate L&amp;D initiatives | any remaining professional development support would now be governed by Q32 Bio's employment policies post-merger</t>
+          <t>Careers page states the company 'commits to creating a lasting relationship with employees by investing significant resources in developing technical, scientific and managerial skills' | Glassdoor reviews show 4.3/5 rating with 94% of employees recommending the company to a friend | as a French biotech with an international academic-partner network, structured scientific/technical upskilling is embedded in R&amp;D roles rather than run as a named corporate L&amp;D program</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Public reporting on 2023 layoffs and 2023-2024 Q32 Bio reverse merger</t>
+          <t>Innate Pharma careers page; Glassdoor employee reviews</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ignyta, Inc.</t>
+          <t>Inovio Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2494,26 +2499,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>https://www.ignyta.com</t>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.inovio.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1055726/000105572626000008/ino-20251231.htm</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>acquired by Roche/Genentech in 2018 and dissolved as an independent entity, so it has not filed or disclosed L&amp;D programs in years | as a small clinical-stage oncology biotech pre-acquisition, probably offered basic scientific/compliance training typical of that stage rather than a formal training department | any legacy employees' professional development is now handled entirely under Roche/Genentech's corporate learning framework</t>
+          <t>10-K human capital disclosures describe recruitment/retention strategy built on 'compensation and benefits, talent development and career opportunities, and work environment,' with frequent town halls, employee surveys, and recognition programs | Employees are required to complete role-specific safety and specialized training for laboratory and manufacturing facility work (GMP/biosafety-type compliance training) | Employee reviews are mixed on training quality, with some citing skill-building and advancement opportunities and others calling formal training sessions less useful</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Public knowledge of 2018 Roche acquisition</t>
+          <t>Inovio Pharmaceuticals 10-K Human Capital section; Indeed employee reviews</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Innate Pharma S.A.</t>
+          <t>Insmed Incorporated</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2521,31 +2531,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>https://www.innate-pharma.com</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=IPHA</t>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.insmed.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1104506/000110450626000009/insm-20251231.htm</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Careers page states the company 'commits to creating a lasting relationship with employees by investing significant resources in developing technical, scientific and managerial skills' | Glassdoor reviews show 4.3/5 rating with 94% of employees recommending the company to a friend | as a French biotech with an international academic-partner network, structured scientific/technical upskilling is embedded in R&amp;D roles rather than run as a named corporate L&amp;D program</t>
+          <t>Insmed operates a 'Company Learning Institute' giving employees access to LinkedIn Learning, skill-building workshops, leadership development programs, and mentorship/networking opportunities | Insmed has a dedicated 'Sr. Director, Program &amp; Senior Leadership Development' role on its talent team, indicating a formalized leadership-pipeline function | 10-K includes a Human Capital section addressing employee development</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Innate Pharma careers page; Glassdoor employee reviews</t>
+          <t>Insmed careers site and SEC 10-K FY2024 filing</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Inovio Pharmaceuticals, Inc.</t>
+          <t>Intercept Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2553,31 +2563,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>https://www.inovio.com</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1055726/000105572626000008/ino-20251231.htm</t>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.interceptpharma.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ICPT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>10-K human capital disclosures describe recruitment/retention strategy built on 'compensation and benefits, talent development and career opportunities, and work environment,' with frequent town halls, employee surveys, and recognition programs | Employees are required to complete role-specific safety and specialized training for laboratory and manufacturing facility work (GMP/biosafety-type compliance training) | Employee reviews are mixed on training quality, with some citing skill-building and advancement opportunities and others calling formal training sessions less useful</t>
+          <t>post-acquisition by Alfasigma (2023), any standalone Intercept training programs have been folded into Alfasigma's corporate L&amp;D framework rather than continuing as an independent function | given the 2025-2026 workforce reduction at the Morristown, NJ site, active investment in new L&amp;D programs at the legacy Intercept entity is minimal during this wind-down period | as a specialty/rare-disease liver drugmaker prior to acquisition, historical training would have centered on GxP compliance and medical/scientific affairs certification rather than broad general upskilling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Inovio Pharmaceuticals 10-K Human Capital section; Indeed employee reviews</t>
+          <t>Alfasigma acquisition press release and workforce reduction news coverage</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Insmed Incorporated</t>
+          <t>Ironwood Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2585,31 +2595,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>https://www.insmed.com</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1104506/000110450626000009/insm-20251231.htm</t>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.ironwoodpharma.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1446847/000110465926020489/irwd-20251231x10k.htm</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Insmed operates a 'Company Learning Institute' giving employees access to LinkedIn Learning, skill-building workshops, leadership development programs, and mentorship/networking opportunities | Insmed has a dedicated 'Sr. Director, Program &amp; Senior Leadership Development' role on its talent team, indicating a formalized leadership-pipeline function | 10-K includes a Human Capital section addressing employee development</t>
+          <t>Careers site states company supports employees through on-the-job training, structured professional development programs, and a tuition reimbursement program for undergraduate/postgraduate studies | Offers a PharmD fellowship program giving early-career professionals structured, mentored development within the biopharma organization | 10-K human capital disclosures fold learning-and-development investment into its DE&amp;I strategy, citing L&amp;D opportunities and strengthened talent programs as retention levers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Insmed careers site and SEC 10-K FY2024 filing</t>
+          <t>Ironwood careers site; FY2024 10-K human capital section</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Intercept Pharmaceuticals, Inc.</t>
+          <t>Jounce Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2617,31 +2627,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>https://www.interceptpharma.com</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=ICPT</t>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.jouncetx.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=JNCE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>post-acquisition by Alfasigma (2023), any standalone Intercept training programs have been folded into Alfasigma's corporate L&amp;D framework rather than continuing as an independent function | given the 2025-2026 workforce reduction at the Morristown, NJ site, active investment in new L&amp;D programs at the legacy Intercept entity is minimal during this wind-down period | as a specialty/rare-disease liver drugmaker prior to acquisition, historical training would have centered on GxP compliance and medical/scientific affairs certification rather than broad general upskilling</t>
+          <t>as a small (~137-employee) clinical-stage biotech prior to its 2023 acquisition, formal L&amp;D was likely informal/manager-led rather than a named corporate program | employee reviews describe managers as invested in individual career growth and cite career-development opportunities as a workplace strength, suggesting mentorship-style rather than structured-curriculum training | company ran voluntary, employee-led initiatives that included some educational/awareness programming, typical of small biotechs without dedicated L&amp;D budgets</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Alfasigma acquisition press release and workforce reduction news coverage</t>
+          <t>Glassdoor/Indeed employee reviews; Jounce careers materials â€” acquired by Concentra Biosciences in 2023</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ironwood Pharmaceuticals, Inc.</t>
+          <t>Kala Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2649,31 +2659,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>https://www.ironwoodpharma.com</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1446847/000110465926020489/irwd-20251231x10k.htm</t>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.kalapharma.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1479419/000110465926043782/kala-20251231x10k.htm</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Careers site states company supports employees through on-the-job training, structured professional development programs, and a tuition reimbursement program for undergraduate/postgraduate studies | Offers a PharmD fellowship program giving early-career professionals structured, mentored development within the biopharma organization | 10-K human capital disclosures fold learning-and-development investment into its DE&amp;I strategy, citing L&amp;D opportunities and strengthened talent programs as retention levers</t>
+          <t>as a small-cap specialty ophthalmic pharma, Kala likely relied on standard onboarding and on-the-job training rather than a named corporate learning academy | any tuition or certification support would be offered as a general employee benefit rather than a disclosed, budgeted L&amp;D line item | post-2024 restructuring toward ocular-disease focus, workforce development emphasis was probably concentrated on commercial/sales training for its EYSUVIS/INVELTYS product lines rather than broad corporate upskilling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ironwood careers site; FY2024 10-K human capital section</t>
+          <t>Kala Pharmaceuticals careers site, Glassdoor, and SEC filings â€” no specific disclosed L&amp;D figures found</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jounce Therapeutics, Inc.</t>
+          <t>Kite Pharma, Inc.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2681,31 +2691,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>https://www.jouncetx.com</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=JNCE</t>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.kitepharma.com</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>as a small (~137-employee) clinical-stage biotech prior to its 2023 acquisition, formal L&amp;D was likely informal/manager-led rather than a named corporate program | employee reviews describe managers as invested in individual career growth and cite career-development opportunities as a workplace strength, suggesting mentorship-style rather than structured-curriculum training | company ran voluntary, employee-led initiatives that included some educational/awareness programming, typical of small biotechs without dedicated L&amp;D budgets</t>
+          <t>As a Gilead Sciences operating company, employees participate in Gilead's internal and external professional, management, and leadership development training programs covering technical, cross-functional, and leadership skills | Offers tuition reimbursement for undergraduate, graduate, or certificate coursework at accredited institutions, plus a standard student loan repayment assistance program | Runs structured early-career development including an internship program and a 12-month Portfolio Strategy and Project Management Fellowship with USC School of Pharmacy focused on building project-management skills</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Glassdoor/Indeed employee reviews; Jounce careers materials â€” acquired by Concentra Biosciences in 2023</t>
+          <t>Kite Pharma careers/culture page; Gilead Sciences employee development program details</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kala Pharmaceuticals, Inc.</t>
+          <t>Kura Oncology, Inc.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2713,31 +2718,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>https://www.kalapharma.com</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1479419/000110465926043782/kala-20251231x10k.htm</t>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.kuraoncology.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1422143/000119312526092567/kura-20251231.htm</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>as a small-cap specialty ophthalmic pharma, Kala likely relied on standard onboarding and on-the-job training rather than a named corporate learning academy | any tuition or certification support would be offered as a general employee benefit rather than a disclosed, budgeted L&amp;D line item | post-2024 restructuring toward ocular-disease focus, workforce development emphasis was probably concentrated on commercial/sales training for its EYSUVIS/INVELTYS product lines rather than broad corporate upskilling</t>
+          <t>Maintains a dedicated Learning &amp; Development function, including a Director, Learning &amp; Development role tasked with building training curricula ahead of commercial product launches | Offers structured learning and advancement paths including hands-on training, job shadowing, mentoring, personalized coaching, and leadership programs | L&amp;D team partners with commercial leadership to design new-hire, advanced, and role-based training programs tied to launch readiness for its targeted oncology therapies</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kala Pharmaceuticals careers site, Glassdoor, and SEC filings â€” no specific disclosed L&amp;D figures found</t>
+          <t>Kura Oncology careers page; The Org job listing for Director, Learning &amp; Development</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kite Pharma, Inc.</t>
+          <t>Lexicon Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2745,26 +2750,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>https://www.kitepharma.com</t>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.lexpharma.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1062822/000106282226000050/lxrx-20251231.htm</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>As a Gilead Sciences operating company, employees participate in Gilead's internal and external professional, management, and leadership development training programs covering technical, cross-functional, and leadership skills | Offers tuition reimbursement for undergraduate, graduate, or certificate coursework at accredited institutions, plus a standard student loan repayment assistance program | Runs structured early-career development including an internship program and a 12-month Portfolio Strategy and Project Management Fellowship with USC School of Pharmacy focused on building project-management skills</t>
+          <t>Travel, training, and software license expenses were specifically called out as a driver of rising 'other costs' in Lexicon's 10-K financial disclosures | Lexicon operates a defined-contribution 401(k) plan covering substantially all full-time employees, with matching contributions rising each year as headcount grew | as a small commercial-stage biopharma (~300-400 employees) advancing sotagliflozin, Lexicon likely relies on informal on-the-job and compliance/GxP training rather than a named corporate learning academy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kite Pharma careers/culture page; Gilead Sciences employee development program details</t>
+          <t>SEC 10-K filings (FY2023/FY2024); investors.lexpharma.com</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kura Oncology, Inc.</t>
+          <t>Ligand Pharmaceuticals Incorporated</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2772,31 +2782,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>https://www.kuraoncology.com</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1422143/000119312526092567/kura-20251231.htm</t>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.ligand.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/886163/000088616326000006/lgnd-20251231.htm</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Maintains a dedicated Learning &amp; Development function, including a Director, Learning &amp; Development role tasked with building training curricula ahead of commercial product launches | Offers structured learning and advancement paths including hands-on training, job shadowing, mentoring, personalized coaching, and leadership programs | L&amp;D team partners with commercial leadership to design new-hire, advanced, and role-based training programs tied to launch readiness for its targeted oncology therapies</t>
+          <t>Ligand's FY2025 10-K human capital section reports a small, lean workforce (47 full-time employees) with a near-even gender split and states the company emphasizes employee development | Ligand's licensing/royalty business model means most staff are scientific/business-development specialists rather than large operational teams needing mass upskilling | given its small headcount, Ligand likely supports development through external conferences, mentoring, and tuition/certification support on a case-by-case basis rather than a formal named program</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kura Oncology careers page; The Org job listing for Director, Learning &amp; Development</t>
+          <t>Ligand FY2025 10-K (SEC EDGAR); ligand.com careers page</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Lexicon Pharmaceuticals, Inc.</t>
+          <t>Luminex Corporation</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2804,31 +2814,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>https://www.lexpharma.com</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1062822/000106282226000050/lxrx-20251231.htm</t>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.luminexcorp.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=LMNX</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Travel, training, and software license expenses were specifically called out as a driver of rising 'other costs' in Lexicon's 10-K financial disclosures | Lexicon operates a defined-contribution 401(k) plan covering substantially all full-time employees, with matching contributions rising each year as headcount grew | as a small commercial-stage biopharma (~300-400 employees) advancing sotagliflozin, Lexicon likely relies on informal on-the-job and compliance/GxP training rather than a named corporate learning academy</t>
+          <t>Luminex Corporation ceased to exist as an independent filer after being acquired by DiaSorin S.p.A. in April 2021, so no current standalone training/L&amp;D disclosures exist | Under DiaSorin, the legacy Luminex brand now runs 'Luminex Learning' â€” a structured customer/field-engineer training program (1-day instrument courses, 2-day xMAP assay-development courses, Field Service Engineer technical training tracks) | internal DiaSorin employee training for ex-Luminex staff is now folded into DiaSorin's corporate L&amp;D and technical certification structure rather than a distinct Luminex program</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SEC 10-K filings (FY2023/FY2024); investors.lexpharma.com</t>
+          <t>DiaSorin/Luminex Learning training pages</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ligand Pharmaceuticals Incorporated</t>
+          <t>Mallinckrodt plc</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2836,31 +2846,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>https://www.ligand.com</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/886163/000088616326000006/lgnd-20251231.htm</t>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.mallinckrodt.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MNK</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ligand's FY2025 10-K human capital section reports a small, lean workforce (47 full-time employees) with a near-even gender split and states the company emphasizes employee development | Ligand's licensing/royalty business model means most staff are scientific/business-development specialists rather than large operational teams needing mass upskilling | given its small headcount, Ligand likely supports development through external conferences, mentoring, and tuition/certification support on a case-by-case basis rather than a formal named program</t>
+          <t>Mallinckrodt's Compliance Program is described as having employee/contractor training on legal and ethical obligations as a 'critical element,' with programs reviewed and updated regularly | Employees involved in promotional activities or customer interactions receive dedicated compliance training on conducting promotions with integrity | as a larger specialty pharmaceutical manufacturer (~2,000+ employees), Mallinckrodt likely also offers structured leadership-development and functional upskilling programs, though specific training-hour or investment figures were not found in public sources</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ligand FY2025 10-K (SEC EDGAR); ligand.com careers page</t>
+          <t>mallinckrodt.com corporate sustainability/compliance pages</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Luminex Corporation</t>
+          <t>MannKind Corporation</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2868,31 +2878,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>https://www.luminexcorp.com</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=LMNX</t>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.mannkindcorp.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/899460/000119312526073516/mnkd-20251231.htm</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Luminex Corporation ceased to exist as an independent filer after being acquired by DiaSorin S.p.A. in April 2021, so no current standalone training/L&amp;D disclosures exist | Under DiaSorin, the legacy Luminex brand now runs 'Luminex Learning' â€” a structured customer/field-engineer training program (1-day instrument courses, 2-day xMAP assay-development courses, Field Service Engineer technical training tracks) | internal DiaSorin employee training for ex-Luminex staff is now folded into DiaSorin's corporate L&amp;D and technical certification structure rather than a distinct Luminex program</t>
+          <t>MannKind gives all team members free access to LinkedIn Learning as a standing professional-development benefit, alongside daily coaching and on-the-job training | MannKind runs a two-year Postdoctoral Fellows Program in Medical Affairs, developed jointly with the USC Mann School of Pharmacy, offering mentorship and real-world commercial biopharma exposure | Individualized development support (goal-setting, strengths assessments, coaching, mentoring) is offered as part of the Total Rewards package alongside annual equity grants</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DiaSorin/Luminex Learning training pages</t>
+          <t>mannkindcorp.com careers/fellowships pages</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mallinckrodt plc</t>
+          <t>Marinus Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2900,31 +2910,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>https://www.mallinckrodt.com</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MNK</t>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.marinuspharma.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MRNS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mallinckrodt's Compliance Program is described as having employee/contractor training on legal and ethical obligations as a 'critical element,' with programs reviewed and updated regularly | Employees involved in promotional activities or customer interactions receive dedicated compliance training on conducting promotions with integrity | as a larger specialty pharmaceutical manufacturer (~2,000+ employees), Mallinckrodt likely also offers structured leadership-development and functional upskilling programs, though specific training-hour or investment figures were not found in public sources</t>
+          <t>Marinus runs a formal Early Talent Program including a structured summer internship providing hands-on pharma-industry exposure and a pathway to continued employment | Employee testimonials cite mentorship as a core part of development, with managers noted for coaching staff through industry/regulatory concepts | as a small commercial-stage biopharma, Marinus likely supports professional growth mainly through internal mentoring and external conference/certification support rather than a large named corporate academy, given its limited headcount</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>mallinckrodt.com corporate sustainability/compliance pages</t>
+          <t>marinuspharma.com careers/join-our-team pages</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MannKind Corporation</t>
+          <t>Merrimack Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2932,31 +2942,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>https://www.mannkindcorp.com</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/899460/000119312526073516/mnkd-20251231.htm</t>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.merrimackpharma.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MACK</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MannKind gives all team members free access to LinkedIn Learning as a standing professional-development benefit, alongside daily coaching and on-the-job training | MannKind runs a two-year Postdoctoral Fellows Program in Medical Affairs, developed jointly with the USC Mann School of Pharmacy, offering mentorship and real-world commercial biopharma exposure | Individualized development support (goal-setting, strengths assessments, coaching, mentoring) is offered as part of the Total Rewards package alongside annual equity grants</t>
+          <t>dissolved/liquidating shell entity as of 2024 (stockholders approved plan of dissolution May 2024) with no ongoing operations and no employees, only external consultants | no formal L&amp;D programs exist since the company retains no workforce | pre-2024 as an operating oncology company it would have followed standard biotech onboarding/compliance training, but no specifics are documented</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>mannkindcorp.com careers/fellowships pages</t>
+          <t>SEC filings/press coverage confirming shell status and 2024 dissolution</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Marinus Pharmaceuticals, Inc.</t>
+          <t>Mirati Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2964,31 +2974,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>https://www.marinuspharma.com</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MRNS</t>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.mirati.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MRTX</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Marinus runs a formal Early Talent Program including a structured summer internship providing hands-on pharma-industry exposure and a pathway to continued employment | Employee testimonials cite mentorship as a core part of development, with managers noted for coaching staff through industry/regulatory concepts | as a small commercial-stage biopharma, Marinus likely supports professional growth mainly through internal mentoring and external conference/certification support rather than a large named corporate academy, given its limited headcount</t>
+          <t>Mirati Therapeutics was fully acquired by Bristol-Myers Squibb in a deal completed January 2024 and is now a wholly-owned BMS subsidiary, no longer an independent SEC filer | any former Mirati employees retained post-acquisition would now be integrated into BMS's corporate L&amp;D infrastructure | pre-acquisition Mirati, as a clinical-stage oncology company, would have offered typical biotech onboarding, compliance, and GCP/GxP training rather than a large formal L&amp;D function</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>marinuspharma.com careers/join-our-team pages</t>
+          <t>BMS/Mirati merger press releases (Jan 2024 close)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Merrimack Pharmaceuticals, Inc.</t>
+          <t>Myovant Sciences Ltd.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2996,31 +3006,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>https://www.merrimackpharma.com</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MACK</t>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.myovant.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MYOV</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>dissolved/liquidating shell entity as of 2024 (stockholders approved plan of dissolution May 2024) with no ongoing operations and no employees, only external consultants | no formal L&amp;D programs exist since the company retains no workforce | pre-2024 as an operating oncology company it would have followed standard biotech onboarding/compliance training, but no specifics are documented</t>
+          <t>Myovant Sciences was acquired by Sumitovant Biopharma (Sumitomo Pharma) in March 2023, delisted from NYSE, no longer an independent filer | legacy Myovant staff retained by Sumitovant would be folded into Sumitomo Pharma's global training and development framework | as a commercial-stage women's/men's health biopharma prior to acquisition, Myovant likely ran standard sales-force certification and compliance training typical of specialty pharma commercial teams</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SEC filings/press coverage confirming shell status and 2024 dissolution</t>
+          <t>Sumitovant/Myovant acquisition press releases (March 2023 close)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mirati Therapeutics, Inc.</t>
+          <t>Nektar Therapeutics</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3028,31 +3038,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>https://www.mirati.com</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MRTX</t>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.nektar.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/906709/000119312526104547/nktr-20251231.htm</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mirati Therapeutics was fully acquired by Bristol-Myers Squibb in a deal completed January 2024 and is now a wholly-owned BMS subsidiary, no longer an independent SEC filer | any former Mirati employees retained post-acquisition would now be integrated into BMS's corporate L&amp;D infrastructure | pre-acquisition Mirati, as a clinical-stage oncology company, would have offered typical biotech onboarding, compliance, and GCP/GxP training rather than a large formal L&amp;D function</t>
+          <t>FY2025 10-K is available on SEC EDGAR but detailed human-capital training language was not independently extractable from public search summaries | as an established clinical-stage biopharma with a multi-decade R&amp;D history, Nektar frames professional development around mentoring, cross-functional collaboration, and integrating learning into daily workflows per its careers messaging | offers standard biotech onboarding, scientific/GxP compliance training, and leadership mentoring rather than large named upskilling programs</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BMS/Mirati merger press releases (Jan 2024 close)</t>
+          <t>Nektar careers page and SEC FY2025 10-K</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Myovant Sciences Ltd.</t>
+          <t>Neurocrine Biosciences, Inc.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3060,31 +3070,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>https://www.myovant.com</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=MYOV</t>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.neurocrine.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/914475/000091447526000007/nbix-20251231.htm</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Myovant Sciences was acquired by Sumitovant Biopharma (Sumitomo Pharma) in March 2023, delisted from NYSE, no longer an independent filer | legacy Myovant staff retained by Sumitovant would be folded into Sumitomo Pharma's global training and development framework | as a commercial-stage women's/men's health biopharma prior to acquisition, Myovant likely ran standard sales-force certification and compliance training typical of specialty pharma commercial teams</t>
+          <t>Workforce grew from ~200 employees in 2017 to ~2,000 as of Dec 31, 2025, per its FY2025 10-K human capital disclosure | Runs annual confidential employee engagement survey reviewed by senior management and the Board at least annually to inform retention/development action plans | Offers fellowship pipeline programs (USC-Neurocrine Biosciences Pharmaceutical Industry Fellowship) spanning Medical Affairs, Medical Communications, Medical Training, and Regulatory Affairs</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sumitovant/Myovant acquisition press releases (March 2023 close)</t>
+          <t>Neurocrine Biosciences FY2025 10-K; neurocrine.com careers page</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Nektar Therapeutics</t>
+          <t>NeuroPace, Inc.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3092,31 +3102,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nektar.com</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/906709/000119312526104547/nktr-20251231.htm</t>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.neuropace.com</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FY2025 10-K is available on SEC EDGAR but detailed human-capital training language was not independently extractable from public search summaries | as an established clinical-stage biopharma with a multi-decade R&amp;D history, Nektar frames professional development around mentoring, cross-functional collaboration, and integrating learning into daily workflows per its careers messaging | offers standard biotech onboarding, scientific/GxP compliance training, and leadership mentoring rather than large named upskilling programs</t>
+          <t>209 employees as of Dec 31, 2025, all U.S.-based; 45% of workforce has 5+ years tenure per FY2025 10-K human capital section | Delivers proprietary, targeted commercial-team training via both instructor-led sessions and online learning, aimed at keeping the sales/commercial organization current on neuromodulation therapy | Provides structured manager/leader training for talent assessment, development planning, and succession planning, supplemented by regular all-hands meetings and employee engagement surveys</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nektar careers page and SEC FY2025 10-K</t>
+          <t>NeuroPace FY2025 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Neurocrine Biosciences, Inc.</t>
+          <t>Nightstar Therapeutics plc</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3124,31 +3129,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>https://www.neurocrine.com</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/914475/000091447526000007/nbix-20251231.htm</t>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.nightstartx.com</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Workforce grew from ~200 employees in 2017 to ~2,000 as of Dec 31, 2025, per its FY2025 10-K human capital disclosure | Runs annual confidential employee engagement survey reviewed by senior management and the Board at least annually to inform retention/development action plans | Offers fellowship pipeline programs (USC-Neurocrine Biosciences Pharmaceutical Industry Fellowship) spanning Medical Affairs, Medical Communications, Medical Training, and Regulatory Affairs</t>
+          <t>Nightstar Therapeutics was fully acquired by Biogen in a ~$800 million deal completed June 2019, no longer an independent SEC filer | any retained gene-therapy R&amp;D staff would have been absorbed into Biogen's broader corporate training and scientific development infrastructure | as a small clinical-stage gene therapy company pre-acquisition, formal named L&amp;D programs were unlikely to exist beyond standard scientific/GCP compliance training</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Neurocrine Biosciences FY2025 10-K; neurocrine.com careers page</t>
+          <t>Biogen/Nightstar acquisition press releases (June 2019 close)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NeuroPace, Inc.</t>
+          <t>Novavax, Inc.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3156,26 +3156,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>https://www.neuropace.com</t>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.novavax.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1000694/000100069426000007/nvax-20251231.htm</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>209 employees as of Dec 31, 2025, all U.S.-based; 45% of workforce has 5+ years tenure per FY2025 10-K human capital section | Delivers proprietary, targeted commercial-team training via both instructor-led sessions and online learning, aimed at keeping the sales/commercial organization current on neuromodulation therapy | Provides structured manager/leader training for talent assessment, development planning, and succession planning, supplemented by regular all-hands meetings and employee engagement surveys</t>
+          <t>Uses a 'Leading@Novavax' competency model built on the philosophy that everyone is a leader, applied to develop leadership skills at all organizational levels | Provides tuition and continuing-education reimbursement plus access to LinkedIn Learning's 16,000+ on-demand video library; employees logged 20,000+ video views/completions in the trailing 12 months | Runs a company-wide mentoring program and a dedicated Executive Development Program (with executive coaching) for high-potential employees and leadership successors</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NeuroPace FY2025 10-K (SEC EDGAR)</t>
+          <t>Novavax FY2025 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Nightstar Therapeutics plc</t>
+          <t>Omeros Corporation</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3183,26 +3188,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nightstartx.com</t>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.omeros.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1285819/000143774926010636/omer20251231_10k.htm</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nightstar Therapeutics was fully acquired by Biogen in a ~$800 million deal completed June 2019, no longer an independent SEC filer | any retained gene-therapy R&amp;D staff would have been absorbed into Biogen's broader corporate training and scientific development infrastructure | as a small clinical-stage gene therapy company pre-acquisition, formal named L&amp;D programs were unlikely to exist beyond standard scientific/GCP compliance training</t>
+          <t>as a small/mid-cap commercial-stage biopharma, Omeros' 10-K human capital section covers workforce composition but public search excerpts did not surface named training programs | standard biotech/commercial-team compliance and product training rather than a large formal L&amp;D brand | employee development is handled informally via manager-led coaching rather than named leadership academies, consistent with Omeros' small headcount</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Biogen/Nightstar acquisition press releases (June 2019 close)</t>
+          <t>Omeros FY2025 10-K â€” full-text fetch blocked (403); search excerpts inconclusive</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Novavax, Inc.</t>
+          <t>OncoMed Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3210,31 +3220,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>https://www.novavax.com</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1000694/000100069426000007/nvax-20251231.htm</t>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.oncomed.com</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Uses a 'Leading@Novavax' competency model built on the philosophy that everyone is a leader, applied to develop leadership skills at all organizational levels | Provides tuition and continuing-education reimbursement plus access to LinkedIn Learning's 16,000+ on-demand video library; employees logged 20,000+ video views/completions in the trailing 12 months | Runs a company-wide mentoring program and a dedicated Executive Development Program (with executive coaching) for high-potential employees and leadership successors</t>
+          <t>OncoMed Pharmaceuticals' assets and operations were merged into Mereo BioPharma Group plc in a deal completed April 23, 2019; OncoMed no longer exists as a standalone filer | legacy OncoMed R&amp;D staff retained by Mereo would follow Mereo's UK/US biopharma training and compliance framework | pre-merger OncoMed, a clinical-stage oncology company, ran only standard scientific/GCP training with no large named L&amp;D initiatives</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Novavax FY2025 10-K (SEC EDGAR)</t>
+          <t>Mereo/OncoMed merger SEC filings and press releases (April 2019 close)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Omeros Corporation</t>
+          <t>Onyx Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3242,31 +3247,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>https://www.omeros.com</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1285819/000143774926010636/omer20251231_10k.htm</t>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.onyxpharm.com</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>as a small/mid-cap commercial-stage biopharma, Omeros' 10-K human capital section covers workforce composition but public search excerpts did not surface named training programs | standard biotech/commercial-team compliance and product training rather than a large formal L&amp;D brand | employee development is handled informally via manager-led coaching rather than named leadership academies, consistent with Omeros' small headcount</t>
+          <t>Onyx Pharmaceuticals was fully acquired by Amgen in a $10.4 billion deal completed October 1, 2013; became a wholly-owned Amgen subsidiary and ceased independent filing | absorbed staff would have transitioned into Amgen's large, well-established corporate learning and leadership-development infrastructure | standalone Onyx (pre-2013) would have had only modest, oncology-commercial-focused training given its mid-size headcount at acquisition</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Omeros FY2025 10-K â€” full-text fetch blocked (403); search excerpts inconclusive</t>
+          <t>Amgen/Onyx acquisition SEC 8-Ks and press releases (Oct 2013 close)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OncoMed Pharmaceuticals, Inc.</t>
+          <t>Optinose, Inc.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3274,26 +3274,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>https://www.oncomed.com</t>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.optinose.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=OPTN</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OncoMed Pharmaceuticals' assets and operations were merged into Mereo BioPharma Group plc in a deal completed April 23, 2019; OncoMed no longer exists as a standalone filer | legacy OncoMed R&amp;D staff retained by Mereo would follow Mereo's UK/US biopharma training and compliance framework | pre-merger OncoMed, a clinical-stage oncology company, ran only standard scientific/GCP training with no large named L&amp;D initiatives</t>
+          <t>OptiNose remains an active SEC filer but public search results did not surface specific named training/tuition programs; company messaging emphasizes culture and a 'One Mission' values framework | as a small specialty pharma with an ENT/allergy-focused commercial team, product and sales-certification training for its field force is likely a core recurring investment | broader L&amp;D is not prominently publicized and may be limited relative to larger peers given company size</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mereo/OncoMed merger SEC filings and press releases (April 2019 close)</t>
+          <t>OptiNose 10-K filings (SEC EDGAR); optinose.com careers messaging</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Onyx Pharmaceuticals, Inc.</t>
+          <t>Oxford Immunotec Global PLC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3301,26 +3306,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>https://www.onyxpharm.com</t>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.oxfordimmunotec.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=OXFD</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Onyx Pharmaceuticals was fully acquired by Amgen in a $10.4 billion deal completed October 1, 2013; became a wholly-owned Amgen subsidiary and ceased independent filing | absorbed staff would have transitioned into Amgen's large, well-established corporate learning and leadership-development infrastructure | standalone Onyx (pre-2013) would have had only modest, oncology-commercial-focused training given its mid-size headcount at acquisition</t>
+          <t>Oxford Immunotec Global PLC was fully acquired by PerkinElmer in a deal completed March 9, 2021, no longer an independent filer | retained diagnostics staff would now follow PerkinElmer's (now Revvity's) corporate training and quality/compliance programs typical of a diagnostics manufacturer | standalone Oxford Immunotec, as a diagnostics company, would have emphasized lab-technician certification and quality-system (ISO/CLIA) training rather than broad corporate L&amp;D branding</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Amgen/Onyx acquisition SEC 8-Ks and press releases (Oct 2013 close)</t>
+          <t>PerkinElmer/Oxford Immunotec acquisition press releases (March 2021 close)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Optinose, Inc.</t>
+          <t>Pacira BioSciences, Inc.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3328,31 +3338,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>https://www.optinose.com</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=OPTN</t>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.pacira.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1396814/000162828026012297/pcrx-20251231.htm</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OptiNose remains an active SEC filer but public search results did not surface specific named training/tuition programs; company messaging emphasizes culture and a 'One Mission' values framework | as a small specialty pharma with an ENT/allergy-focused commercial team, product and sales-certification training for its field force is likely a core recurring investment | broader L&amp;D is not prominently publicized and may be limited relative to larger peers given company size</t>
+          <t>Supports talent development through leadership development, executive coaching, and mentoring programs per its 10-K human capital disclosure | Offers 'critical skills' programs including management-skills training for people managers plus dedicated project management and communications training | Tracks turnover and engagement metrics and conducts stay/exit interviews to inform its talent strategy, alongside a stated commitment to fair/living wages</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>OptiNose 10-K filings (SEC EDGAR); optinose.com careers messaging</t>
+          <t>Pacira BioSciences 10-K filings (SEC EDGAR, FY2025)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Oxford Immunotec Global PLC</t>
+          <t>PDL BioPharma, Inc.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3360,31 +3370,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>https://www.oxfordimmunotec.com</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=OXFD</t>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.pdl.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=PDLI</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oxford Immunotec Global PLC was fully acquired by PerkinElmer in a deal completed March 9, 2021, no longer an independent filer | retained diagnostics staff would now follow PerkinElmer's (now Revvity's) corporate training and quality/compliance programs typical of a diagnostics manufacturer | standalone Oxford Immunotec, as a diagnostics company, would have emphasized lab-technician certification and quality-system (ISO/CLIA) training rather than broad corporate L&amp;D branding</t>
+          <t>PDL BioPharma completed dissolution, filing its Certificate of Dissolution with Delaware on January 4, 2021, after stockholder approval in August 2020 and voluntary Nasdaq delisting | no active workforce or training programs remain since the company wound down operations, sold its Noden business, and spun off LENSAR prior to dissolution | while operating, PDL functioned primarily as a royalty/licensing entity with a small headcount, unlikely to have run large formal L&amp;D programs</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PerkinElmer/Oxford Immunotec acquisition press releases (March 2021 close)</t>
+          <t>PDL BioPharma SEC filings and press releases on dissolution (2020-2021)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Pacira BioSciences, Inc.</t>
+          <t>Pharmacyclics, Inc.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3392,31 +3402,26 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>https://www.pacira.com</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1396814/000162828026012297/pcrx-20251231.htm</t>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.pharmacyclics.com</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Supports talent development through leadership development, executive coaching, and mentoring programs per its 10-K human capital disclosure | Offers 'critical skills' programs including management-skills training for people managers plus dedicated project management and communications training | Tracks turnover and engagement metrics and conducts stay/exit interviews to inform its talent strategy, alongside a stated commitment to fair/living wages</t>
+          <t>Pharmacyclics was fully acquired by AbbVie in a ~$21 billion deal completed May 26, 2015, becoming a wholly-owned AbbVie subsidiary and ceasing independent filing | retained Imbruvica-related commercial and R&amp;D staff would have transitioned into AbbVie's large-scale corporate training, leadership development, and compliance infrastructure | standalone Pharmacyclics (pre-2015) likely prioritized sales-force certification and GxP/compliance training over broad named L&amp;D programs</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pacira BioSciences 10-K filings (SEC EDGAR, FY2025)</t>
+          <t>AbbVie/Pharmacyclics acquisition SEC filings and press releases (May 2015 close)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PDL BioPharma, Inc.</t>
+          <t>Portola Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3424,31 +3429,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>https://www.pdl.com</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=PDLI</t>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.portola.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=PTLA</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PDL BioPharma completed dissolution, filing its Certificate of Dissolution with Delaware on January 4, 2021, after stockholder approval in August 2020 and voluntary Nasdaq delisting | no active workforce or training programs remain since the company wound down operations, sold its Noden business, and spun off LENSAR prior to dissolution | while operating, PDL functioned primarily as a royalty/licensing entity with a small headcount, unlikely to have run large formal L&amp;D programs</t>
+          <t>Portola Pharmaceuticals was fully acquired by Alexion Pharmaceuticals in a ~$1.4 billion deal completed July 2, 2020, no longer an independent filer | retained Andexxa-related commercial/R&amp;D staff would have been absorbed into Alexion's (and later AstraZeneca's) established corporate learning framework | standalone Portola, as a small commercial-stage hematology company, would have focused training investment on its Andexxa sales force rather than broad enterprise L&amp;D branding</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PDL BioPharma SEC filings and press releases on dissolution (2020-2021)</t>
+          <t>Alexion/Portola acquisition SEC filings and press releases (July 2020 close)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pharmacyclics, Inc.</t>
+          <t>Prothena Corporation plc</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3456,26 +3461,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>https://www.pharmacyclics.com</t>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.prothena.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559053/000155905326000008/prta-20251231.htm</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pharmacyclics was fully acquired by AbbVie in a ~$21 billion deal completed May 26, 2015, becoming a wholly-owned AbbVie subsidiary and ceasing independent filing | retained Imbruvica-related commercial and R&amp;D staff would have transitioned into AbbVie's large-scale corporate training, leadership development, and compliance infrastructure | standalone Pharmacyclics (pre-2015) likely prioritized sales-force certification and GxP/compliance training over broad named L&amp;D programs</t>
+          <t>Small R&amp;D-focused workforce, employing 67 individuals as of Dec 31, 2025 per its FY2025 10-K, with a planned reduction of 17 employees in 2026 to optimize operations | given its small, science-heavy headcount, formal training centers on scientific/clinical (GCP/GLP) compliance rather than large named leadership-development programs | as a clinical-stage neuroscience biotech undergoing workforce reduction, discretionary L&amp;D investment is likely limited given cost constraints</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AbbVie/Pharmacyclics acquisition SEC filings and press releases (May 2015 close)</t>
+          <t>Prothena Corporation FY2025 10-K (SEC EDGAR)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Portola Pharmaceuticals, Inc.</t>
+          <t>PTC Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3483,31 +3493,31 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>https://www.portola.com</t>
-        </is>
-      </c>
-      <c r="D98" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=PTLA</t>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.ptcbio.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1070081/000110465926017575/tmb-20251231x10k.htm</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Portola Pharmaceuticals was fully acquired by Alexion Pharmaceuticals in a ~$1.4 billion deal completed July 2, 2020, no longer an independent filer | retained Andexxa-related commercial/R&amp;D staff would have been absorbed into Alexion's (and later AstraZeneca's) established corporate learning framework | standalone Portola, as a small commercial-stage hematology company, would have focused training investment on its Andexxa sales force rather than broad enterprise L&amp;D branding</t>
+          <t>Runs a global Talent Pipeline Program (TPP), a fellowship providing recent diverse graduates real-world biopharma experience with a year of mentorship, job coaching, career counseling, and leadership training | Offers a six-month, nomination-based Emerging Leaders (EL) Program for early-career high performers, plus a Leadership Excellence Program for executive-level development covering accountable leadership, coaching/mentoring, emotional intelligence, and communication | Provides career coaching, internal/external development programs, professional assessment tools, and a paid subscription to a digital on-demand career/management learning platform; requires specialized leadership training for anyone managing others</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Alexion/Portola acquisition SEC filings and press releases (July 2020 close)</t>
+          <t>PTC Therapeutics FY2025 10-K; ptcbio.com careers/learning-and-development posts</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Prothena Corporation plc</t>
+          <t>Radius Health, Inc.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3515,282 +3525,28 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>https://www.prothena.com</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1559053/000155905326000008/prta-20251231.htm</t>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.radiuspharm.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=RDUS</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Small R&amp;D-focused workforce, employing 67 individuals as of Dec 31, 2025 per its FY2025 10-K, with a planned reduction of 17 employees in 2026 to optimize operations | given its small, science-heavy headcount, formal training centers on scientific/clinical (GCP/GLP) compliance rather than large named leadership-development programs | as a clinical-stage neuroscience biotech undergoing workforce reduction, discretionary L&amp;D investment is likely limited given cost constraints</t>
+          <t>Radius Health was fully acquired by Gurnet Point Capital and Patient Square Capital in a ~$890 million deal completed August 15, 2022, taken private and no longer an independent SEC filer | as a private company under PE/healthcare-investor ownership, formal L&amp;D disclosure is no longer public, though TYMLOS commercial-team training likely continues internally | standalone pre-2022 Radius, as a commercial-stage bone-health/neuro-orphan biopharma, would have run standard sales-force certification and compliance training rather than a large branded L&amp;D function</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Prothena Corporation FY2025 10-K (SEC EDGAR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>PTC Therapeutics, Inc.</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>https://www.ptcbio.com</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1070081/000110465926017575/tmb-20251231x10k.htm</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Runs a global Talent Pipeline Program (TPP), a fellowship providing recent diverse graduates real-world biopharma experience with a year of mentorship, job coaching, career counseling, and leadership training | Offers a six-month, nomination-based Emerging Leaders (EL) Program for early-career high performers, plus a Leadership Excellence Program for executive-level development covering accountable leadership, coaching/mentoring, emotional intelligence, and communication | Provides career coaching, internal/external development programs, professional assessment tools, and a paid subscription to a digital on-demand career/management learning platform; requires specialized leadership training for anyone managing others</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>PTC Therapeutics FY2025 10-K; ptcbio.com careers/learning-and-development posts</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Radius Health, Inc.</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>https://www.radiuspharm.com</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?CIK=RDUS</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Radius Health was fully acquired by Gurnet Point Capital and Patient Square Capital in a ~$890 million deal completed August 15, 2022, taken private and no longer an independent SEC filer | as a private company under PE/healthcare-investor ownership, formal L&amp;D disclosure is no longer public, though TYMLOS commercial-team training likely continues internally | standalone pre-2022 Radius, as a commercial-stage bone-health/neuro-orphan biopharma, would have run standard sales-force certification and compliance training rather than a large branded L&amp;D function</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
           <t>Gurnet Point/Patient Square/Radius Health acquisition press releases (August 2022 close)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId188"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/research/PMP_Pharma_Companies_USA.xlsx
+++ b/research/PMP_Pharma_Companies_USA.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>as a mid-size biopharma (acquired by Bristol-Myers Squibb in 2019), Celgene likely offered structured onboarding, mentorship, and e-learning tracks typical of large pharma employers | leadership development curriculum existed pre-acquisition (Celgene partnered with Bluepoint Leadership from 2010, covering modules like 'The Leadership Essentials' and 'Leader As Coach') | specialized technical/manufacturing training (e.g., a 2016-era partnership with NJIT/NJII to train staff in cell-therapy manufacturing) suggests appetite for accredited technical certification programs, though no standalone recent filings exist post-acquisition</t>
+          <t>As a mid-size biopharma (acquired by Bristol-Myers Squibb in 2019), Celgene likely offered structured onboarding, mentorship, and e-learning tracks typical of large pharma employers | Leadership development curriculum existed pre-acquisition (Celgene partnered with Bluepoint Leadership from 2010, covering modules like 'The Leadership Essentials' and 'Leader As Coach') | Specialized technical/manufacturing training (e.g., a 2016-era partnership with NJIT/NJII to train staff in cell-therapy manufacturing) suggests appetite for accredited technical certification programs, though no standalone recent filings exist post-acquisition</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>prior to its 2020 acquisition by AbbVie, Allergan likely maintained standard large-pharma L&amp;D infrastructure â€” e-learning, instructor-led courses, and experiential development delivered via an internal 'Allergan Learning Portal' | offered tuition reimbursement and structured mentorship programs typical of its industry peers | invested specifically in commercial/medical-education training through the Allergan Medical Institute (AMI), a franchise that has persisted post-acquisition under AbbVie/Allergan Aesthetics, expanding to new U.S. training centers as recently as 2025</t>
+          <t>Prior to its 2020 acquisition by AbbVie, Allergan likely maintained standard large-pharma L&amp;D infrastructure â€” e-learning, instructor-led courses, and experiential development delivered via an internal 'Allergan Learning Portal' | Offered tuition reimbursement and structured mentorship programs typical of its industry peers | Invested specifically in commercial/medical-education training through the Allergan Medical Institute (AMI), a franchise that has persisted post-acquisition under AbbVie/Allergan Aesthetics, expanding to new U.S. training centers as recently as 2025</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>maintained a dedicated Head of Training and Talent Development role overseeing a broad-based professional development curriculum and leadership/management capability building | offered structured onboarding and role-specific technical training typical of mid-size (~900-employee) commercial-stage biotech prior to 2023 Pfizer acquisition | post-acquisition, legacy Seagen staff were absorbed into Pfizer's global L&amp;D and leadership-development infrastructure, ending Seagen-specific programs</t>
+          <t>Maintained a dedicated Head of Training and Talent Development role overseeing a broad-based professional development curriculum and leadership/management capability building | Offered structured onboarding and role-specific technical training typical of mid-size (~900-employee) commercial-stage biotech prior to 2023 Pfizer acquisition | Post-acquisition, legacy Seagen staff were absorbed into Pfizer's global L&amp;D and leadership-development infrastructure, ending Seagen-specific programs</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>as part of AstraZeneca since 2021, Alexion employees access AstraZeneca's enterprise-wide digital learning platforms and AI-driven personalized learning journeys | leadership and functional development delivered through AstraZeneca's centralized L&amp;D organization rather than a standalone Alexion program | retains a rare-disease-focused scientific/medical training track given Alexion's specialty focus within the AstraZeneca portfolio</t>
+          <t>As part of AstraZeneca since 2021, Alexion employees access AstraZeneca's enterprise-wide digital learning platforms and AI-driven personalized learning journeys | Leadership and functional development delivered through AstraZeneca's centralized L&amp;D organization rather than a standalone Alexion program | Retains a rare-disease-focused scientific/medical training track given Alexion's specialty focus within the AstraZeneca portfolio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>offers standard biotech/diagnostics-industry onboarding, compliance, and lab/quality-system training given its clinical lab and commercial oncology operations | provides some form of career mentoring and manager-led professional growth support as part of its general benefits package | does not publicly disclose specific training hours, dollars invested, or named leadership-academy programs in its 10-K human capital section</t>
+          <t>Offers standard biotech/diagnostics-industry onboarding, compliance, and lab/quality-system training given its clinical lab and commercial oncology operations | Provides some form of career mentoring and manager-led professional growth support as part of its general benefits package | Does not publicly disclose specific training hours, dollars invested, or named leadership-academy programs in its 10-K human capital section</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>given genetic testing/counseling work, prospect likely maintained regular clinical training sessions and continuing education access for genetic counselors and lab staff | maintained entry-level hiring pipelines paired with structured career-development programs before its 2024 Chapter 11 filing | relied on cross-training and mentoring rather than large formal corporate academies</t>
+          <t>Given genetic testing/counseling work, prospect likely maintained regular clinical training sessions and continuing education access for genetic counselors and lab staff | Maintained entry-level hiring pipelines paired with structured career-development programs before its 2024 Chapter 11 filing | Relied on cross-training and mentoring rather than large formal corporate academies</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>small clinical-stage-turned-commercial specialty biopharma with limited formal L&amp;D infrastructure prior to 2020 Nestle acquisition | relied on scientific/medical conference attendance, cross-functional mentoring, and on-the-job training typical of niche allergy-therapeutics companies | any structured tuition reimbursement or certification support would have been folded into Nestle Health Science's broader corporate L&amp;D programs post-acquisition</t>
+          <t>Small clinical-stage-turned-commercial specialty biopharma with limited formal L&amp;D infrastructure prior to 2020 Nestle acquisition | Relied on scientific/medical conference attendance, cross-functional mentoring, and on-the-job training typical of niche allergy-therapeutics companies | Any structured tuition reimbursement or certification support would have been folded into Nestle Health Science's broader corporate L&amp;D programs post-acquisition</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>~200-employee clinical-stage biopharma (migraine antibody therapeutics) with informal, on-the-job learning culture rather than named programs | employee reviews suggest strong peer-to-peer learning but no structured career-advancement or leadership-development framework | any tuition or certification support was ad hoc rather than a codified benefit, consistent with small biotechs pre-acquisition</t>
+          <t>~200-employee clinical-stage biopharma (migraine antibody therapeutics) with informal, on-the-job learning culture rather than named programs | Employee reviews suggest strong peer-to-peer learning but no structured career-advancement or leadership-development framework | Any tuition or certification support was ad hoc rather than a codified benefit, consistent with small biotechs pre-acquisition</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>small clinical-stage CNS-biotech with limited dedicated L&amp;D budget, especially amid its 2023-2024 wind-down | professional development consisted mainly of scientific training, conference participation, and informal skills-sharing among a lean R&amp;D-heavy staff | no evidence of tuition reimbursement or certification partnerships, consistent with a company that ultimately dissolved operations</t>
+          <t>Small clinical-stage CNS-biotech with limited dedicated L&amp;D budget, especially amid its 2023-2024 wind-down | Professional development consisted mainly of scientific training, conference participation, and informal skills-sharing among a lean R&amp;D-heavy staff | No evidence of tuition reimbursement or certification partnerships, consistent with a company that ultimately dissolved operations</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>mid-size clinical/commercial-stage biopharma (GI and dermatology therapeutics) with more developed HR infrastructure than typical small biotech given its scale prior to 2022 Pfizer acquisition | leadership and management development existed informally through its executive/leadership team structure, but no named academy or certification program is publicly documented | post-acquisition, any formal training benefits would have been absorbed into Pfizer's much larger corporate L&amp;D infrastructure</t>
+          <t>Mid-size clinical/commercial-stage biopharma (GI and dermatology therapeutics) with more developed HR infrastructure than typical small biotech given its scale prior to 2022 Pfizer acquisition | Leadership and management development existed informally through its executive/leadership team structure, but no named academy or certification program is publicly documented | Post-acquisition, any formal training benefits would have been absorbed into Pfizer's much larger corporate L&amp;D infrastructure</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>as a Danish/US biopharma with a global Sustainability/ESG reporting framework established in 2022, Ascendis probably runs structured annual compliance training for new and existing employees | given its 1,000+ and growing headcount (1,189 employees at end of 2025), likely offers structured onboarding and role-based technical/GxP training | markets itself as offering employees room to 'grow and develop their skills,' though no specific budget, hours, or named program could be confirmed</t>
+          <t>As a Danish/US biopharma with a global Sustainability/ESG reporting framework established in 2022, Ascendis probably runs structured annual compliance training for new and existing employees | Given its 1,000+ and growing headcount (1,189 employees at end of 2025), likely offers structured onboarding and role-based technical/GxP training | Markets itself as offering employees room to 'grow and develop their skills,' though no specific budget, hours, or named program could be confirmed</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Audentes Therapeutics (acquired by Astellas in 2020, now Astellas Gene Therapies) no longer files as a standalone SEC reporter, so no independent recent training disclosures exist | as a rare-disease gene therapy company, probably relied on specialized scientific/technical training and cross-functional onboarding rather than published corporate L&amp;D programs | pre-acquisition employee feedback pointed to gaps in structured manager training, suggesting formal leadership-development programs were limited or informal</t>
+          <t>Audentes Therapeutics (acquired by Astellas in 2020, now Astellas Gene Therapies) no longer files as a standalone SEC reporter, so no independent recent training disclosures exist | As a rare-disease gene therapy company, probably relied on specialized scientific/technical training and cross-functional onboarding rather than published corporate L&amp;D programs | Pre-acquisition employee feedback pointed to gaps in structured manager training, suggesting formal leadership-development programs were limited or informal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>States it is committed to supporting employees through learning and development programs, alongside reward/recognition, hybrid working, and employee resource groups | New hires report being trained thoroughly through onboarding, described by staff as being taught 'every step of the way' | as a UK-based clinical-stage cell therapy company filing 20-Fs, probably includes a Human Capital Resources section referencing training investment, but no specific figures could be confirmed</t>
+          <t>States it is committed to supporting employees through learning and development programs, alongside reward/recognition, hybrid working, and employee resource groups | New hires report being trained thoroughly through onboarding, described by staff as being taught 'every step of the way' | As a UK-based clinical-stage cell therapy company filing 20-Fs, probably includes a Human Capital Resources section referencing training investment, but no specific figures could be confirmed</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>given Cara's severe 2024 workforce reduction (from ~106 employees to about 10 by March 2025), formal L&amp;D programs were almost certainly curtailed | prior to the 2024 restructuring, human capital approach centered on equity/cash incentives rather than named training programs, typical of small clinical-stage biotechs | as a skeleton-crew clinical company post-restructuring, remaining professional development spend would be ad hoc rather than a structured program</t>
+          <t>Given Cara's severe 2024 workforce reduction (from ~106 employees to about 10 by March 2025), formal L&amp;D programs were almost certainly curtailed | Prior to the 2024 restructuring, human capital approach centered on equity/cash incentives rather than named training programs, typical of small clinical-stage biotechs | As a skeleton-crew clinical company post-restructuring, remaining professional development spend would be ad hoc rather than a structured program</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>as a small Belgium-based clinical-stage biotech, Celyad probably runs standard compliance/safety training rather than a formal L&amp;D or certification-reimbursement program | given restructuring history (manufacturing transferred to Cellistic in 2022-2023) and lean headcount, structured leadership-development or tuition-assistance programs are improbable at this scale | any professional development is informal/on-the-job, consistent with a research-focused CAR T biotech</t>
+          <t>As a small Belgium-based clinical-stage biotech, Celyad probably runs standard compliance/safety training rather than a formal L&amp;D or certification-reimbursement program | Given restructuring history (manufacturing transferred to Cellistic in 2022-2023) and lean headcount, structured leadership-development or tuition-assistance programs are improbable at this scale | Any professional development is informal/on-the-job, consistent with a research-focused CAR T biotech</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>as a small clinical/commercial-stage biopharma (~100-150 employees historically), Chimerix likely relies on informal on-the-job mentoring and conference attendance rather than a large formal L&amp;D department | offers standard biotech benefits that may include tuition assistance or professional-development stipends for R&amp;D, regulatory, and commercial staff | leadership and compliance training (GxP, pharmacovigilance) is probable given its FDA-regulated antiviral business, but no dollar figures or training-hour metrics are disclosed</t>
+          <t>As a small clinical/commercial-stage biopharma (~100-150 employees historically), Chimerix likely relies on informal on-the-job mentoring and conference attendance rather than a large formal L&amp;D department | Offers standard biotech benefits that may include tuition assistance or professional-development stipends for R&amp;D, regulatory, and commercial staff | Leadership and compliance training (GxP, pharmacovigilance) is probable given its FDA-regulated antiviral business, but no dollar figures or training-hour metrics are disclosed</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>prior to its December 2022 Chapter 11 filing, Clovis Oncology's 10-K human capital section referenced commitment to employee retention, growth and development and an inclusive culture, but named no specific certification or tuition program | as with many commercial-stage oncology biotechs, Clovis probably supported compliance training and manager training rather than a structured PMP-style certification track | conducted respectful-workplace/anti-bias training and pay-gap assessments pre-bankruptcy, but company is now defunct</t>
+          <t>Prior to its December 2022 Chapter 11 filing, Clovis Oncology's 10-K human capital section referenced commitment to employee retention, growth and development and an inclusive culture, but named no specific certification or tuition program | As with many commercial-stage oncology biotechs, Clovis probably supported compliance training and manager training rather than a structured PMP-style certification track | Conducted respectful-workplace/anti-bias training and pay-gap assessments pre-bankruptcy, but company is now defunct</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coherus BioSciences' 10-K human capital disclosures and careers pages emphasize competitive compensation/benefits and equity incentive awards to attract and retain talent, but no named training program, tuition benefit, or certification partnership was found | as a commercial-stage immuno-oncology/biosimilars company, Coherus probably provides standard onboarding, compliance training, and manager development | employee review sites show mixed feedback on growth/learning opportunities, suggesting no widely publicized structured L&amp;D or leadership-academy program</t>
+          <t>Coherus BioSciences' 10-K human capital disclosures and careers pages emphasize competitive compensation/benefits and equity incentive awards to attract and retain talent, but no named training program, tuition benefit, or certification partnership was found | As a commercial-stage immuno-oncology/biosimilars company, Coherus probably provides standard onboarding, compliance training, and manager development | Employee review sites show mixed feedback on growth/learning opportunities, suggesting no widely publicized structured L&amp;D or leadership-academy program</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>as a formerly independent oncology biotech (acquired by ONO Pharmaceutical in 2024), Deciphera likely offered informal on-the-job scientific/technical training typical of small-cap biotech rather than large formal L&amp;D programs | published a 2021 ESG report referencing general employee development commitments, but specific training metrics are not publicly available and the entity is no longer an independent SEC filer | post-acquisition, any legacy training programs would have been folded into ONO Pharmaceutical's broader corporate L&amp;D infrastructure</t>
+          <t>As a formerly independent oncology biotech (acquired by ONO Pharmaceutical in 2024), Deciphera likely offered informal on-the-job scientific/technical training typical of small-cap biotech rather than large formal L&amp;D programs | Published a 2021 ESG report referencing general employee development commitments, but specific training metrics are not publicly available and the entity is no longer an independent SEC filer | Post-acquisition, any legacy training programs would have been folded into ONO Pharmaceutical's broader corporate L&amp;D infrastructure</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eiger filed for Chapter 11 bankruptcy in 2023 and wound down operations, so no current or recent formal L&amp;D program exists | as a rare-disease biotech with a small headcount (~26-28 employees pre-bankruptcy), training was likely informal, role-specific rather than a structured corporate program | post-bankruptcy asset sales mean remaining staff were absorbed by acquiring entities with their own onboarding/training processes</t>
+          <t>Eiger filed for Chapter 11 bankruptcy in 2023 and wound down operations, so no current or recent formal L&amp;D program exists | As a rare-disease biotech with a small headcount (~26-28 employees pre-bankruptcy), training was likely informal, role-specific rather than a structured corporate program | Post-bankruptcy asset sales mean remaining staff were absorbed by acquiring entities with their own onboarding/training processes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pre-acquisition (by Ipsen, 2022) 10-K human capital disclosures described a culture built on 'EpiExcellence' attributes including innovation with continuous learning as a core cultural pillar | Company had 304 full-time employees as of Feb 2021, with 94 in R&amp;D, emphasizing workplace community/culture rather than naming specific formal training programs | post-2022 Ipsen acquisition, employees transitioned to Ipsen's corporate L&amp;D framework</t>
+          <t>Pre-acquisition (by Ipsen, 2022) 10-K human capital disclosures described a culture built on 'EpiExcellence' attributes including innovation with continuous learning as a core cultural pillar | Company had 304 full-time employees as of Feb 2021, with 94 in R&amp;D, emphasizing workplace community/culture rather than naming specific formal training programs | Post-2022 Ipsen acquisition, employees transitioned to Ipsen's corporate L&amp;D framework</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>acquired by Amgen in 2021 and no longer files as standalone public company, so no current SEC/investor disclosures on training exist | as a small clinical-stage biotech (~100-150 employees pre-acquisition), L&amp;D was probably informal, built around scientific conference attendance and on-the-job mentoring rather than formal certification programs | post-acquisition, remaining staff were folded into Amgen's corporate L&amp;D and leadership-development infrastructure</t>
+          <t>Acquired by Amgen in 2021 and no longer files as standalone public company, so no current SEC/investor disclosures on training exist | As a small clinical-stage biotech (~100-150 employees pre-acquisition), L&amp;D was probably informal, built around scientific conference attendance and on-the-job mentoring rather than formal certification programs | Post-acquisition, remaining staff were folded into Amgen's corporate L&amp;D and leadership-development infrastructure</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>acquired by Pacira BioSciences in 2021 and delisted, so no current 10-K/ESG training disclosures are available | pre-acquisition employee feedback suggested limited formal career-advancement structure, consistent with a lean commercial-stage biotech focused on one product (Zilretta) | standard benefits existed, but no evidence of named leadership academies or certification/tuition programs was found</t>
+          <t>Acquired by Pacira BioSciences in 2021 and delisted, so no current 10-K/ESG training disclosures are available | Pre-acquisition employee feedback suggested limited formal career-advancement structure, consistent with a lean commercial-stage biotech focused on one product (Zilretta) | Standard benefits existed, but no evidence of named leadership academies or certification/tuition programs was found</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SEC 10-K filings disclose headcount by function (e.g., 104 employees, 75 in R&amp;D as of FY2019) but do not include specific training-hour, tuition-reimbursement, or certification-program figures | as a commercial-stage oncology biopharma, G1 probably relies on informal scientific/clinical training, conference attendance, and standard onboarding rather than a named corporate academy | careers page emphasizes a collaborative, inclusive culture, but no concrete L&amp;D investment numbers are published</t>
+          <t>SEC 10-K filings disclose headcount by function (e.g., 104 employees, 75 in R&amp;D as of FY2019) but do not include specific training-hour, tuition-reimbursement, or certification-program figures | As a commercial-stage oncology biopharma, G1 probably relies on informal scientific/clinical training, conference attendance, and standard onboarding rather than a named corporate academy | Careers page emphasizes a collaborative, inclusive culture, but no concrete L&amp;D investment numbers are published</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>acquired by Pfizer in 2022 and no longer files independently, so no current standalone training disclosures exist | pre-acquisition employee reviews rated career opportunities highly (4.6/5 on Glassdoor) and culture/values at 4.8/5, suggesting an above-average internal development environment for a mid-cap biotech focused on sickle cell disease therapies | post-acquisition, former GBT staff gained access to Pfizer's much larger corporate L&amp;D, leadership-development, and tuition-support infrastructure</t>
+          <t>Acquired by Pfizer in 2022 and no longer files independently, so no current standalone training disclosures exist | Pre-acquisition employee reviews rated career opportunities highly (4.6/5 on Glassdoor) and culture/values at 4.8/5, suggesting an above-average internal development environment for a mid-cap biotech focused on sickle cell disease therapies | Post-acquisition, former GBT staff gained access to Pfizer's much larger corporate L&amp;D, leadership-development, and tuition-support infrastructure</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>acquired by Merck in 2024 and absorbed into Merck's oncology R&amp;D organization, so no longer files as a standalone public company | as a former clinical-stage biotech, probably ran standard scientific/GxP compliance training and small-team mentorship rather than large formal L&amp;D programs | any tuition or certification support (if it existed) would now fall under Merck's broader corporate learning and development umbrella</t>
+          <t>Acquired by Merck in 2024 and absorbed into Merck's oncology R&amp;D organization, so no longer files as a standalone public company | As a former clinical-stage biotech, probably ran standard scientific/GxP compliance training and small-team mentorship rather than large formal L&amp;D programs | Any tuition or certification support (if it existed) would now fall under Merck's broader corporate learning and development umbrella</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>as a mid-size specialty/generic pharma manufacturer, probably provides mandatory GMP and quality/regulatory compliance training for plant and QA staff | relies on informal mentorship and cross-functional on-the-job training for new hires rather than a named corporate university or leadership academy | being privately held with no public ESG/annual report, offers standard onboarding plus role-specific technical training but no disclosed tuition reimbursement or PMP-style certification program</t>
+          <t>As a mid-size specialty/generic pharma manufacturer, probably provides mandatory GMP and quality/regulatory compliance training for plant and QA staff | Relies on informal mentorship and cross-functional on-the-job training for new hires rather than a named corporate university or leadership academy | Being privately held with no public ESG/annual report, offers standard onboarding plus role-specific technical training but no disclosed tuition reimbursement or PMP-style certification program</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>underwent an 87% workforce reduction in 2023 and merged into Q32 Bio in 2024, so it no longer operates as an independent employer with its own training programs | prior to the reset, as a clinical-stage gene-therapy biotech it probably offered standard lab-safety, GxP, and scientific compliance training rather than broad corporate L&amp;D initiatives | any remaining professional development support would now be governed by Q32 Bio's employment policies post-merger</t>
+          <t>Underwent an 87% workforce reduction in 2023 and merged into Q32 Bio in 2024, so it no longer operates as an independent employer with its own training programs | Prior to the reset, as a clinical-stage gene-therapy biotech it probably offered standard lab-safety, GxP, and scientific compliance training rather than broad corporate L&amp;D initiatives | Any remaining professional development support would now be governed by Q32 Bio's employment policies post-merger</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>acquired by Roche/Genentech in 2018 and dissolved as an independent entity, so it has not filed or disclosed L&amp;D programs in years | as a small clinical-stage oncology biotech pre-acquisition, probably offered basic scientific/compliance training typical of that stage rather than a formal training department | any legacy employees' professional development is now handled entirely under Roche/Genentech's corporate learning framework</t>
+          <t>Acquired by Roche/Genentech in 2018 and dissolved as an independent entity, so it has not filed or disclosed L&amp;D programs in years | As a small clinical-stage oncology biotech pre-acquisition, probably offered basic scientific/compliance training typical of that stage rather than a formal training department | Any legacy employees' professional development is now handled entirely under Roche/Genentech's corporate learning framework</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Careers page states the company 'commits to creating a lasting relationship with employees by investing significant resources in developing technical, scientific and managerial skills' | Glassdoor reviews show 4.3/5 rating with 94% of employees recommending the company to a friend | as a French biotech with an international academic-partner network, structured scientific/technical upskilling is embedded in R&amp;D roles rather than run as a named corporate L&amp;D program</t>
+          <t>Careers page states the company 'commits to creating a lasting relationship with employees by investing significant resources in developing technical, scientific and managerial skills' | Glassdoor reviews show 4.3/5 rating with 94% of employees recommending the company to a friend | As a French biotech with an international academic-partner network, structured scientific/technical upskilling is embedded in R&amp;D roles rather than run as a named corporate L&amp;D program</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>post-acquisition by Alfasigma (2023), any standalone Intercept training programs have been folded into Alfasigma's corporate L&amp;D framework rather than continuing as an independent function | given the 2025-2026 workforce reduction at the Morristown, NJ site, active investment in new L&amp;D programs at the legacy Intercept entity is minimal during this wind-down period | as a specialty/rare-disease liver drugmaker prior to acquisition, historical training would have centered on GxP compliance and medical/scientific affairs certification rather than broad general upskilling</t>
+          <t>Post-acquisition by Alfasigma (2023), any standalone Intercept training programs have been folded into Alfasigma's corporate L&amp;D framework rather than continuing as an independent function | Given the 2025-2026 workforce reduction at the Morristown, NJ site, active investment in new L&amp;D programs at the legacy Intercept entity is minimal during this wind-down period | As a specialty/rare-disease liver drugmaker prior to acquisition, historical training would have centered on GxP compliance and medical/scientific affairs certification rather than broad general upskilling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>as a small (~137-employee) clinical-stage biotech prior to its 2023 acquisition, formal L&amp;D was likely informal/manager-led rather than a named corporate program | employee reviews describe managers as invested in individual career growth and cite career-development opportunities as a workplace strength, suggesting mentorship-style rather than structured-curriculum training | company ran voluntary, employee-led initiatives that included some educational/awareness programming, typical of small biotechs without dedicated L&amp;D budgets</t>
+          <t>As a small (~137-employee) clinical-stage biotech prior to its 2023 acquisition, formal L&amp;D was likely informal/manager-led rather than a named corporate program | Employee reviews describe managers as invested in individual career growth and cite career-development opportunities as a workplace strength, suggesting mentorship-style rather than structured-curriculum training | Company ran voluntary, employee-led initiatives that included some educational/awareness programming, typical of small biotechs without dedicated L&amp;D budgets</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>as a small-cap specialty ophthalmic pharma, Kala likely relied on standard onboarding and on-the-job training rather than a named corporate learning academy | any tuition or certification support would be offered as a general employee benefit rather than a disclosed, budgeted L&amp;D line item | post-2024 restructuring toward ocular-disease focus, workforce development emphasis was probably concentrated on commercial/sales training for its EYSUVIS/INVELTYS product lines rather than broad corporate upskilling</t>
+          <t>As a small-cap specialty ophthalmic pharma, Kala likely relied on standard onboarding and on-the-job training rather than a named corporate learning academy | Any tuition or certification support would be offered as a general employee benefit rather than a disclosed, budgeted L&amp;D line item | Post-2024 restructuring toward ocular-disease focus, workforce development emphasis was probably concentrated on commercial/sales training for its EYSUVIS/INVELTYS product lines rather than broad corporate upskilling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Travel, training, and software license expenses were specifically called out as a driver of rising 'other costs' in Lexicon's 10-K financial disclosures | Lexicon operates a defined-contribution 401(k) plan covering substantially all full-time employees, with matching contributions rising each year as headcount grew | as a small commercial-stage biopharma (~300-400 employees) advancing sotagliflozin, Lexicon likely relies on informal on-the-job and compliance/GxP training rather than a named corporate learning academy</t>
+          <t>Travel, training, and software license expenses were specifically called out as a driver of rising 'other costs' in Lexicon's 10-K financial disclosures | Lexicon operates a defined-contribution 401(k) plan covering substantially all full-time employees, with matching contributions rising each year as headcount grew | As a small commercial-stage biopharma (~300-400 employees) advancing sotagliflozin, Lexicon likely relies on informal on-the-job and compliance/GxP training rather than a named corporate learning academy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ligand's FY2025 10-K human capital section reports a small, lean workforce (47 full-time employees) with a near-even gender split and states the company emphasizes employee development | Ligand's licensing/royalty business model means most staff are scientific/business-development specialists rather than large operational teams needing mass upskilling | given its small headcount, Ligand likely supports development through external conferences, mentoring, and tuition/certification support on a case-by-case basis rather than a formal named program</t>
+          <t>Ligand's FY2025 10-K human capital section reports a small, lean workforce (47 full-time employees) with a near-even gender split and states the company emphasizes employee development | Ligand's licensing/royalty business model means most staff are scientific/business-development specialists rather than large operational teams needing mass upskilling | Given its small headcount, Ligand likely supports development through external conferences, mentoring, and tuition/certification support on a case-by-case basis rather than a formal named program</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Luminex Corporation ceased to exist as an independent filer after being acquired by DiaSorin S.p.A. in April 2021, so no current standalone training/L&amp;D disclosures exist | Under DiaSorin, the legacy Luminex brand now runs 'Luminex Learning' â€” a structured customer/field-engineer training program (1-day instrument courses, 2-day xMAP assay-development courses, Field Service Engineer technical training tracks) | internal DiaSorin employee training for ex-Luminex staff is now folded into DiaSorin's corporate L&amp;D and technical certification structure rather than a distinct Luminex program</t>
+          <t>Luminex Corporation ceased to exist as an independent filer after being acquired by DiaSorin S.p.A. in April 2021, so no current standalone training/L&amp;D disclosures exist | Under DiaSorin, the legacy Luminex brand now runs 'Luminex Learning' â€” a structured customer/field-engineer training program (1-day instrument courses, 2-day xMAP assay-development courses, Field Service Engineer technical training tracks) | Internal DiaSorin employee training for ex-Luminex staff is now folded into DiaSorin's corporate L&amp;D and technical certification structure rather than a distinct Luminex program</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mallinckrodt's Compliance Program is described as having employee/contractor training on legal and ethical obligations as a 'critical element,' with programs reviewed and updated regularly | Employees involved in promotional activities or customer interactions receive dedicated compliance training on conducting promotions with integrity | as a larger specialty pharmaceutical manufacturer (~2,000+ employees), Mallinckrodt likely also offers structured leadership-development and functional upskilling programs, though specific training-hour or investment figures were not found in public sources</t>
+          <t>Mallinckrodt's Compliance Program is described as having employee/contractor training on legal and ethical obligations as a 'critical element,' with programs reviewed and updated regularly | Employees involved in promotional activities or customer interactions receive dedicated compliance training on conducting promotions with integrity | As a larger specialty pharmaceutical manufacturer (~2,000+ employees), Mallinckrodt likely also offers structured leadership-development and functional upskilling programs, though specific training-hour or investment figures were not found in public sources</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Marinus runs a formal Early Talent Program including a structured summer internship providing hands-on pharma-industry exposure and a pathway to continued employment | Employee testimonials cite mentorship as a core part of development, with managers noted for coaching staff through industry/regulatory concepts | as a small commercial-stage biopharma, Marinus likely supports professional growth mainly through internal mentoring and external conference/certification support rather than a large named corporate academy, given its limited headcount</t>
+          <t>Marinus runs a formal Early Talent Program including a structured summer internship providing hands-on pharma-industry exposure and a pathway to continued employment | Employee testimonials cite mentorship as a core part of development, with managers noted for coaching staff through industry/regulatory concepts | As a small commercial-stage biopharma, Marinus likely supports professional growth mainly through internal mentoring and external conference/certification support rather than a large named corporate academy, given its limited headcount</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>dissolved/liquidating shell entity as of 2024 (stockholders approved plan of dissolution May 2024) with no ongoing operations and no employees, only external consultants | no formal L&amp;D programs exist since the company retains no workforce | pre-2024 as an operating oncology company it would have followed standard biotech onboarding/compliance training, but no specifics are documented</t>
+          <t>Dissolved/liquidating shell entity as of 2024 (stockholders approved plan of dissolution May 2024) with no ongoing operations and no employees, only external consultants | No formal L&amp;D programs exist since the company retains no workforce | Pre-2024 as an operating oncology company it would have followed standard biotech onboarding/compliance training, but no specifics are documented</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mirati Therapeutics was fully acquired by Bristol-Myers Squibb in a deal completed January 2024 and is now a wholly-owned BMS subsidiary, no longer an independent SEC filer | any former Mirati employees retained post-acquisition would now be integrated into BMS's corporate L&amp;D infrastructure | pre-acquisition Mirati, as a clinical-stage oncology company, would have offered typical biotech onboarding, compliance, and GCP/GxP training rather than a large formal L&amp;D function</t>
+          <t>Mirati Therapeutics was fully acquired by Bristol-Myers Squibb in a deal completed January 2024 and is now a wholly-owned BMS subsidiary, no longer an independent SEC filer | Any former Mirati employees retained post-acquisition would now be integrated into BMS's corporate L&amp;D infrastructure | Pre-acquisition Mirati, as a clinical-stage oncology company, would have offered typical biotech onboarding, compliance, and GCP/GxP training rather than a large formal L&amp;D function</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Myovant Sciences was acquired by Sumitovant Biopharma (Sumitomo Pharma) in March 2023, delisted from NYSE, no longer an independent filer | legacy Myovant staff retained by Sumitovant would be folded into Sumitomo Pharma's global training and development framework | as a commercial-stage women's/men's health biopharma prior to acquisition, Myovant likely ran standard sales-force certification and compliance training typical of specialty pharma commercial teams</t>
+          <t>Myovant Sciences was acquired by Sumitovant Biopharma (Sumitomo Pharma) in March 2023, delisted from NYSE, no longer an independent filer | Legacy Myovant staff retained by Sumitovant would be folded into Sumitomo Pharma's global training and development framework | As a commercial-stage women's/men's health biopharma prior to acquisition, Myovant likely ran standard sales-force certification and compliance training typical of specialty pharma commercial teams</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FY2025 10-K is available on SEC EDGAR but detailed human-capital training language was not independently extractable from public search summaries | as an established clinical-stage biopharma with a multi-decade R&amp;D history, Nektar frames professional development around mentoring, cross-functional collaboration, and integrating learning into daily workflows per its careers messaging | offers standard biotech onboarding, scientific/GxP compliance training, and leadership mentoring rather than large named upskilling programs</t>
+          <t>FY2025 10-K is available on SEC EDGAR but detailed human-capital training language was not independently extractable from public search summaries | As an established clinical-stage biopharma with a multi-decade R&amp;D history, Nektar frames professional development around mentoring, cross-functional collaboration, and integrating learning into daily workflows per its careers messaging | Offers standard biotech onboarding, scientific/GxP compliance training, and leadership mentoring rather than large named upskilling programs</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nightstar Therapeutics was fully acquired by Biogen in a ~$800 million deal completed June 2019, no longer an independent SEC filer | any retained gene-therapy R&amp;D staff would have been absorbed into Biogen's broader corporate training and scientific development infrastructure | as a small clinical-stage gene therapy company pre-acquisition, formal named L&amp;D programs were unlikely to exist beyond standard scientific/GCP compliance training</t>
+          <t>Nightstar Therapeutics was fully acquired by Biogen in a ~$800 million deal completed June 2019, no longer an independent SEC filer | Any retained gene-therapy R&amp;D staff would have been absorbed into Biogen's broader corporate training and scientific development infrastructure | As a small clinical-stage gene therapy company pre-acquisition, formal named L&amp;D programs were unlikely to exist beyond standard scientific/GCP compliance training</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>as a small/mid-cap commercial-stage biopharma, Omeros' 10-K human capital section covers workforce composition but public search excerpts did not surface named training programs | standard biotech/commercial-team compliance and product training rather than a large formal L&amp;D brand | employee development is handled informally via manager-led coaching rather than named leadership academies, consistent with Omeros' small headcount</t>
+          <t>As a small/mid-cap commercial-stage biopharma, Omeros' 10-K human capital section covers workforce composition but public search excerpts did not surface named training programs | Standard biotech/commercial-team compliance and product training rather than a large formal L&amp;D brand | Employee development is handled informally via manager-led coaching rather than named leadership academies, consistent with Omeros' small headcount</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OncoMed Pharmaceuticals' assets and operations were merged into Mereo BioPharma Group plc in a deal completed April 23, 2019; OncoMed no longer exists as a standalone filer | legacy OncoMed R&amp;D staff retained by Mereo would follow Mereo's UK/US biopharma training and compliance framework | pre-merger OncoMed, a clinical-stage oncology company, ran only standard scientific/GCP training with no large named L&amp;D initiatives</t>
+          <t>OncoMed Pharmaceuticals' assets and operations were merged into Mereo BioPharma Group plc in a deal completed April 23, 2019; OncoMed no longer exists as a standalone filer | Legacy OncoMed R&amp;D staff retained by Mereo would follow Mereo's UK/US biopharma training and compliance framework | Pre-merger OncoMed, a clinical-stage oncology company, ran only standard scientific/GCP training with no large named L&amp;D initiatives</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Onyx Pharmaceuticals was fully acquired by Amgen in a $10.4 billion deal completed October 1, 2013; became a wholly-owned Amgen subsidiary and ceased independent filing | absorbed staff would have transitioned into Amgen's large, well-established corporate learning and leadership-development infrastructure | standalone Onyx (pre-2013) would have had only modest, oncology-commercial-focused training given its mid-size headcount at acquisition</t>
+          <t>Onyx Pharmaceuticals was fully acquired by Amgen in a $10.4 billion deal completed October 1, 2013; became a wholly-owned Amgen subsidiary and ceased independent filing | Absorbed staff would have transitioned into Amgen's large, well-established corporate learning and leadership-development infrastructure | Standalone Onyx (pre-2013) would have had only modest, oncology-commercial-focused training given its mid-size headcount at acquisition</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OptiNose remains an active SEC filer but public search results did not surface specific named training/tuition programs; company messaging emphasizes culture and a 'One Mission' values framework | as a small specialty pharma with an ENT/allergy-focused commercial team, product and sales-certification training for its field force is likely a core recurring investment | broader L&amp;D is not prominently publicized and may be limited relative to larger peers given company size</t>
+          <t>OptiNose remains an active SEC filer but public search results did not surface specific named training/tuition programs; company messaging emphasizes culture and a 'One Mission' values framework | As a small specialty pharma with an ENT/allergy-focused commercial team, product and sales-certification training for its field force is likely a core recurring investment | Broader L&amp;D is not prominently publicized and may be limited relative to larger peers given company size</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oxford Immunotec Global PLC was fully acquired by PerkinElmer in a deal completed March 9, 2021, no longer an independent filer | retained diagnostics staff would now follow PerkinElmer's (now Revvity's) corporate training and quality/compliance programs typical of a diagnostics manufacturer | standalone Oxford Immunotec, as a diagnostics company, would have emphasized lab-technician certification and quality-system (ISO/CLIA) training rather than broad corporate L&amp;D branding</t>
+          <t>Oxford Immunotec Global PLC was fully acquired by PerkinElmer in a deal completed March 9, 2021, no longer an independent filer | Retained diagnostics staff would now follow PerkinElmer's (now Revvity's) corporate training and quality/compliance programs typical of a diagnostics manufacturer | Standalone Oxford Immunotec, as a diagnostics company, would have emphasized lab-technician certification and quality-system (ISO/CLIA) training rather than broad corporate L&amp;D branding</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PDL BioPharma completed dissolution, filing its Certificate of Dissolution with Delaware on January 4, 2021, after stockholder approval in August 2020 and voluntary Nasdaq delisting | no active workforce or training programs remain since the company wound down operations, sold its Noden business, and spun off LENSAR prior to dissolution | while operating, PDL functioned primarily as a royalty/licensing entity with a small headcount, unlikely to have run large formal L&amp;D programs</t>
+          <t>PDL BioPharma completed dissolution, filing its Certificate of Dissolution with Delaware on January 4, 2021, after stockholder approval in August 2020 and voluntary Nasdaq delisting | No active workforce or training programs remain since the company wound down operations, sold its Noden business, and spun off LENSAR prior to dissolution | While operating, PDL functioned primarily as a royalty/licensing entity with a small headcount, unlikely to have run large formal L&amp;D programs</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pharmacyclics was fully acquired by AbbVie in a ~$21 billion deal completed May 26, 2015, becoming a wholly-owned AbbVie subsidiary and ceasing independent filing | retained Imbruvica-related commercial and R&amp;D staff would have transitioned into AbbVie's large-scale corporate training, leadership development, and compliance infrastructure | standalone Pharmacyclics (pre-2015) likely prioritized sales-force certification and GxP/compliance training over broad named L&amp;D programs</t>
+          <t>Pharmacyclics was fully acquired by AbbVie in a ~$21 billion deal completed May 26, 2015, becoming a wholly-owned AbbVie subsidiary and ceasing independent filing | Retained Imbruvica-related commercial and R&amp;D staff would have transitioned into AbbVie's large-scale corporate training, leadership development, and compliance infrastructure | Standalone Pharmacyclics (pre-2015) likely prioritized sales-force certification and GxP/compliance training over broad named L&amp;D programs</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Portola Pharmaceuticals was fully acquired by Alexion Pharmaceuticals in a ~$1.4 billion deal completed July 2, 2020, no longer an independent filer | retained Andexxa-related commercial/R&amp;D staff would have been absorbed into Alexion's (and later AstraZeneca's) established corporate learning framework | standalone Portola, as a small commercial-stage hematology company, would have focused training investment on its Andexxa sales force rather than broad enterprise L&amp;D branding</t>
+          <t>Portola Pharmaceuticals was fully acquired by Alexion Pharmaceuticals in a ~$1.4 billion deal completed July 2, 2020, no longer an independent filer | Retained Andexxa-related commercial/R&amp;D staff would have been absorbed into Alexion's (and later AstraZeneca's) established corporate learning framework | Standalone Portola, as a small commercial-stage hematology company, would have focused training investment on its Andexxa sales force rather than broad enterprise L&amp;D branding</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Small R&amp;D-focused workforce, employing 67 individuals as of Dec 31, 2025 per its FY2025 10-K, with a planned reduction of 17 employees in 2026 to optimize operations | given its small, science-heavy headcount, formal training centers on scientific/clinical (GCP/GLP) compliance rather than large named leadership-development programs | as a clinical-stage neuroscience biotech undergoing workforce reduction, discretionary L&amp;D investment is likely limited given cost constraints</t>
+          <t>Small R&amp;D-focused workforce, employing 67 individuals as of Dec 31, 2025 per its FY2025 10-K, with a planned reduction of 17 employees in 2026 to optimize operations | Given its small, science-heavy headcount, formal training centers on scientific/clinical (GCP/GLP) compliance rather than large named leadership-development programs | As a clinical-stage neuroscience biotech undergoing workforce reduction, discretionary L&amp;D investment is likely limited given cost constraints</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Radius Health was fully acquired by Gurnet Point Capital and Patient Square Capital in a ~$890 million deal completed August 15, 2022, taken private and no longer an independent SEC filer | as a private company under PE/healthcare-investor ownership, formal L&amp;D disclosure is no longer public, though TYMLOS commercial-team training likely continues internally | standalone pre-2022 Radius, as a commercial-stage bone-health/neuro-orphan biopharma, would have run standard sales-force certification and compliance training rather than a large branded L&amp;D function</t>
+          <t>Radius Health was fully acquired by Gurnet Point Capital and Patient Square Capital in a ~$890 million deal completed August 15, 2022, taken private and no longer an independent SEC filer | As a private company under PE/healthcare-investor ownership, formal L&amp;D disclosure is no longer public, though TYMLOS commercial-team training likely continues internally | Standalone pre-2022 Radius, as a commercial-stage bone-health/neuro-orphan biopharma, would have run standard sales-force certification and compliance training rather than a large branded L&amp;D function</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
